--- a/markets/fashion/Qatar_Fashion_Stores.xlsx
+++ b/markets/fashion/Qatar_Fashion_Stores.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -612,17 +612,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Balenciaga Qatar</t>
+          <t>American Eagle Qatar</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.balenciaga.com/en-qa</t>
+          <t>https://www.americaneagle.com.qa/</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Salesforce Commerce Cloud</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -642,29 +642,29 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Qatar-locale storefront (en-qa, QAR)</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.balenciaga.com/en-qa</t>
+          <t>https://web.archive.org/web/20250322231222/https://www.americaneagle.com.qa/ar/american-eagle/shop-women/bottoms/shorts/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Bershka Qatar</t>
+          <t>Balenciaga Qatar</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.bershka.com/qa/</t>
+          <t>https://www.balenciaga.com/en-qa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>custom/unknown</t>
+          <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -684,24 +684,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Qatar-locale storefront (en-qa, QAR)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260613215835/https://www.bershka.com/qa/ar/%D8%A7%D9%84%D9%86%D8%B3%D8%A7%D8%A1/%D9%85%D9%84%D8%A7%D8%A8%D8%B3/%D9%81%D8%B3%D8%A7%D8%AA%D9%8A%D9%86-n3802.html</t>
+          <t>https://www.balenciaga.com/en-qa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Burberry Qatar</t>
+          <t>Bershka Qatar</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://qa.burberry.com/</t>
+          <t>https://www.bershka.com/qa/</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>custom/unknown</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -726,29 +726,29 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Qatar-locale storefront (qa.burberry.com); no QAR on homepage</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://qa.burberry.com/</t>
+          <t>https://web.archive.org/web/20260613215835/https://www.bershka.com/qa/ar/%D8%A7%D9%84%D9%86%D8%B3%D8%A7%D8%A1/%D9%85%D9%84%D8%A7%D8%A8%D8%B3/%D9%81%D8%B3%D8%A7%D8%AA%D9%8A%D9%86-n3802.html</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Decathlon Qatar</t>
+          <t>Burberry Qatar</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://decathlon.qa/</t>
+          <t>https://qa.burberry.com/</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -768,24 +768,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Qatar-locale storefront (qa.burberry.com); no QAR on homepage</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://decathlon.qa/</t>
+          <t>https://qa.burberry.com/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Desigual Qatar</t>
+          <t>Calvin Klein Qatar</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.desigual.com/en_QA/</t>
+          <t>https://www.calvinklein.qa/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Salesforce Commerce Cloud</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -810,24 +810,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Known major retailer – manually accepted (403 bot-wall, not bypassed)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.desigual.com/en_QA/</t>
+          <t>https://web.archive.org/web/20251122044217/https://www.calvinklein.qa/ar/kids-black-friday-early.html</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Foot Locker Qatar</t>
+          <t>Carrefour Qatar</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.qa/en/</t>
+          <t>https://www.carrefourqatar.com/mafqat/en/</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -857,24 +857,24 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.qa/en/</t>
+          <t>https://www.carrefourqatar.com/mafqat/en/men-t-shirt/mens-tshirt-ss-plain/p/981282</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Giordano Qatar</t>
+          <t>Centrepoint Qatar</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://giordano.qa/</t>
+          <t>https://www.centrepointstores.com/qa/en/</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -894,39 +894,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://giordano.qa/collections.json</t>
+          <t>https://web.archive.org/web/20220612014351/https://www.centrepointstores.com/qa/en/Women/Clothing/Dresses/SPLASH-Ruched-Printed-Midi-Shift-Dress-with-Short-Sleeves/p/1020622</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Gymshark Qatar</t>
+          <t>Chloé Qatar</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.gymshark.qa/</t>
+          <t>https://www.chloe.com/qa/</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -936,29 +936,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.gymshark.qa/</t>
+          <t>https://www.chloe.com/qa/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lacoste Qatar</t>
+          <t>Decathlon Qatar</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.lacoste.qa/</t>
+          <t>https://decathlon.qa/</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Salesforce Commerce Cloud</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -978,24 +978,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Known major retailer – Qatar storefront (lacoste.qa, QAR)</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.lacoste.qa/</t>
+          <t>https://decathlon.qa/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Mango Qatar</t>
+          <t>Desigual Qatar</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://shop.mango.com/qa/en/</t>
+          <t>https://www.desigual.com/en_QA/</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>custom/unknown</t>
+          <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1020,24 +1020,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260617064834/https://shop.mango.com/qa/ar/c/%D8%A7%D9%84%D8%A7%D8%B7%D9%81%D8%A7%D9%84/%D8%A7%D9%88%D9%84%D8%A7%D8%AF-%D8%B5%D8%BA%D8%A7%D8%B1/%D8%A8%D9%84%D8%A7%D9%8A%D8%B2/9b255289</t>
+          <t>https://www.desigual.com/en_QA/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marks &amp; Spencer Qatar</t>
+          <t>Foot Locker Qatar</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://www.marksandspencer.qa/en/fashion</t>
+          <t>https://www.footlocker.qa/en/</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>custom/unknown</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1062,24 +1062,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.marksandspencerme.com/en-qa/</t>
+          <t>https://www.footlocker.qa/en/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Massimo Dutti Qatar</t>
+          <t>Giordano Qatar</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.massimodutti.com/qa/</t>
+          <t>https://giordano.qa/</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>custom/unknown</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1104,24 +1104,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20261006232223/https://www.massimodutti.com/qa/100-raffia-midsized-tote-bag-l06922605</t>
+          <t>https://giordano.qa/collections.json</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Matalan Qatar</t>
+          <t>Gymshark Qatar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://www.matalanme.com/qa_ar</t>
+          <t>https://www.gymshark.qa/</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>custom/unknown</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1151,24 +1151,24 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.matalanme.com/qa_ar/</t>
+          <t>https://www.gymshark.qa/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Max Fashion Qatar</t>
+          <t>Lacoste Qatar</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.maxfashion.com/qa/en/</t>
+          <t>https://www.lacoste.qa/</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1188,29 +1188,29 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Known major retailer – manually accepted</t>
+          <t>Known major retailer – Qatar storefront (lacoste.qa, QAR)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20250706160300/https://www.maxfashion.com/qa/en/</t>
+          <t>https://www.lacoste.qa/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Muji Qatar</t>
+          <t>Mango Qatar</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.muji.qa/en/</t>
+          <t>https://shop.mango.com/qa/en/</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>custom/unknown</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1235,19 +1235,19 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.muji.qa/en/</t>
+          <t>https://web.archive.org/web/20260617064834/https://shop.mango.com/qa/ar/c/%D8%A7%D9%84%D8%A7%D8%B7%D9%81%D8%A7%D9%84/%D8%A7%D9%88%D9%84%D8%A7%D8%AF-%D8%B5%D8%BA%D8%A7%D8%B1/%D8%A8%D9%84%D8%A7%D9%8A%D8%B2/9b255289</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Next Qatar</t>
+          <t>Marks &amp; Spencer Qatar</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.next.qa/</t>
+          <t>https://www.marksandspencer.qa/en/fashion</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1272,29 +1272,29 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.next.qa/Next-QA-AR-Products-1.xml.gz</t>
+          <t>https://www.marksandspencerme.com/en-qa/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Nike Qatar</t>
+          <t>Massimo Dutti Qatar</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.nike.qa/en/home/</t>
+          <t>https://www.massimodutti.com/qa/</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Salesforce Commerce Cloud</t>
+          <t>custom/unknown</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1314,24 +1314,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.nike.qa/en/home/</t>
+          <t>https://web.archive.org/web/20261006232223/https://www.massimodutti.com/qa/100-raffia-midsized-tote-bag-l06922605</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oysho Qatar</t>
+          <t>Matalan Qatar</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.oysho.com/qa/</t>
+          <t>https://www.matalanme.com/qa_ar</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1356,29 +1356,29 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260712062634/https://www.oysho.com/qa/2-square-piping-hair-claws-l33180414</t>
+          <t>https://www.matalanme.com/qa_ar/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Pull&amp;Bear Qatar</t>
+          <t>Max Fashion Qatar</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.pullandbear.com/qa/</t>
+          <t>https://www.maxfashion.com/qa/en/</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>custom/unknown</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1398,29 +1398,29 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Known major retailer – manually accepted</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260712213550/https://www.pullandbear.com/qa/ar/%D8%A7%D9%84%D8%B1%D8%AC%D8%A7%D9%84/%D9%85%D9%84%D8%A7%D8%A8%D8%B3/anime-n7253?celement=1030378186</t>
+          <t>https://web.archive.org/web/20250706160300/https://www.maxfashion.com/qa/en/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Replay Qatar</t>
+          <t>Muji Qatar</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://replayjeans.qa/</t>
+          <t>https://www.muji.qa/en/</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1440,24 +1440,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://replayjeans.qa/</t>
+          <t>https://www.muji.qa/en/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Riva Fashion</t>
+          <t>Namshi</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://www.rivafashion.com/en-qa/</t>
+          <t>https://www.namshi.com/qatar-en/</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>magento</t>
+          <t>Custom (Next.js)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1482,24 +1482,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.rivafashion.com/en-qa/</t>
+          <t>https://www.namshi.com/qatar-en/buy-2xtremz-textured-dress-with-short-sleeves-and-pockets/Z3B43CABEDCDDD73D9CA8Z/p/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Salam Stores</t>
+          <t>Next Qatar</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://salams.com/</t>
+          <t>https://www.next.qa/</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Magento</t>
+          <t>custom/unknown</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1524,29 +1524,29 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://salams.com/</t>
+          <t>https://www.next.qa/Next-QA-AR-Products-1.xml.gz</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SHEIN</t>
+          <t>Nike Qatar</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://ar.shein.com/</t>
+          <t>https://www.nike.qa/en/home/</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1566,24 +1566,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Known major retailer – manually accepted</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://ar.shein.com/</t>
+          <t>https://www.nike.qa/en/home/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Stradivarius Qatar</t>
+          <t>Ounass Qatar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://www.stradivarius.com/qa/</t>
+          <t>https://www.ounass.qa/</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1593,12 +1593,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>custom/unknown</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1608,24 +1608,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260712091550/https://www.stradivarius.com/qa/d09-super-highwaist-skinny-jeans-l01450741</t>
+          <t>https://www.ounass.qa/shop-emporio-armani-eagle-patch-zip-hoodie-for-kids-00438af14935_4067.html</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Styli Qatar</t>
+          <t>Oysho Qatar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://stylishop.com/qa/en</t>
+          <t>https://www.oysho.com/qa/</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>custom/unknown</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1650,24 +1650,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Qatar-locale storefront (/qa/en); bot-light page, no QAR on homepage</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://stylishop.com/qa/en</t>
+          <t>https://web.archive.org/web/20260712062634/https://www.oysho.com/qa/2-square-piping-hair-claws-l33180414</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Suitsupply</t>
+          <t>PrettyLittleThing Qatar</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://suitsupply.com/en-qa/</t>
+          <t>https://www.prettylittlething.qa/</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Men</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Salesforce Commerce Cloud</t>
+          <t>Custom (Magento)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1692,24 +1692,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Known major retailer – manually accepted (Cloudflare-protected, not bypassed)</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://suitsupply.com/en-qa/</t>
+          <t>https://www.prettylittlething.qa/animal-printed-onion-skin-bandeau-maxi-dress.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sun &amp; Sand Sports Qatar</t>
+          <t>Printemps Doha</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://en-qa.sssports.com/</t>
+          <t>https://www.printemps.com/</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Salesforce Commerce Cloud</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1734,24 +1734,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://en-qa.sssports.com/</t>
+          <t>https://www.printemps.com/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ted Baker Qatar</t>
+          <t>Pull&amp;Bear Qatar</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.tedbaker.qa/</t>
+          <t>https://www.pullandbear.com/qa/</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>custom/unknown</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1776,24 +1776,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.tedbaker.qa/collections.json</t>
+          <t>https://web.archive.org/web/20260712213550/https://www.pullandbear.com/qa/ar/%D8%A7%D9%84%D8%B1%D8%AC%D8%A7%D9%84/%D9%85%D9%84%D8%A7%D8%A8%D8%B3/anime-n7253?celement=1030378186</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Triumph &amp; Sloggi Qatar</t>
+          <t>Replay Qatar</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.shoptriumph.qa/</t>
+          <t>https://replayjeans.qa/</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1823,19 +1823,19 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.shoptriumph.qa/</t>
+          <t>https://replayjeans.qa/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Valentino</t>
+          <t>Riva Fashion</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.valentino.com/en-qa/</t>
+          <t>https://www.rivafashion.com/en-qa/</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>magento</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1860,39 +1860,39 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.valentino.com/en-qa/</t>
+          <t>https://www.rivafashion.com/en-qa/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Victoria's Secret Qatar</t>
+          <t>Salam Stores</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.victoriassecret.com.qa/en/</t>
+          <t>https://salams.com/</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Magento</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1902,29 +1902,29 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.victoriassecret.com.qa/en/</t>
+          <t>https://salams.com/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VogaCloset</t>
+          <t>SHEIN</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://vogacloset.com/qatar/</t>
+          <t>https://ar.shein.com/</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>custom/unknown</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1944,24 +1944,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Verified (secondary evidence)</t>
+          <t>Known major retailer – manually accepted</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260713004429/https://vogacloset.com/qatar/ar/beauty/haircare/hair-treatments/joico-joico-blonde-life-brilliant-glow-brightening-oil-100ml-gsh-mp-jco1103066.html</t>
+          <t>https://ar.shein.com/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Zara Qatar</t>
+          <t>Stradivarius Qatar</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.zara.com/qa/en/</t>
+          <t>https://www.stradivarius.com/qa/</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1991,19 +1991,19 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://web.archive.org/web/20260521053824/https://www.zara.com/qa/ar/%D8%A7%D9%94%D9%81%D8%B1%D9%88%D9%84-%D8%A8%D8%AD%D9%8A%D8%A7%D9%83%D8%A9-%D9%83%D8%B1%D9%88%D8%B4%D9%8A%D9%87-p02209489.html</t>
+          <t>https://web.archive.org/web/20260712091550/https://www.stradivarius.com/qa/d09-super-highwaist-skinny-jeans-l01450741</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ace &amp; Zian Women Clothing</t>
+          <t>Styli Qatar</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://aceandzianwomenclothing.qa/</t>
+          <t>https://stylishop.com/qa/en</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2023,29 +2023,29 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Qatar-locale storefront (/qa/en); bot-light page, no QAR on homepage</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://aceandzianwomenclothing.qa/</t>
+          <t>https://stylishop.com/qa/en</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Afraa Boutique</t>
+          <t>Suitsupply</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://afraaboutique.com/</t>
+          <t>https://suitsupply.com/en-qa/</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2055,81 +2055,81 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Men</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>WooCommerce</t>
+          <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://afraaboutique.com/wp-json/wc/store/v1/products/categories</t>
+          <t>https://suitsupply.com/en-qa/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Almotahajiba</t>
+          <t>Sun &amp; Sand Sports Qatar</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.almotahajiba.com/</t>
+          <t>https://en-qa.sssports.com/</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.almotahajiba.com/</t>
+          <t>https://en-qa.sssports.com/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ami Paris</t>
+          <t>Ted Baker Qatar</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.amiparis.com/en-qa/</t>
+          <t>https://www.tedbaker.qa/</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2149,29 +2149,29 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.amiparis.com/en-qa/</t>
+          <t>https://www.tedbaker.qa/collections.json</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azul</t>
+          <t>Triumph &amp; Sloggi Qatar</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.azul.qa/</t>
+          <t>https://www.shoptriumph.qa/</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2186,34 +2186,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.azul.qa/</t>
+          <t>https://www.shoptriumph.qa/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Balmain</t>
+          <t>Valentino</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://balmain.com/en-qa</t>
+          <t>https://www.valentino.com/en-qa/</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>shopify</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2243,19 +2243,19 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://balmain.com/</t>
+          <t>https://www.valentino.com/en-qa/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Brands Qatar</t>
+          <t>Victoria's Secret Qatar</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://brandsco.qa/</t>
+          <t>https://www.victoriassecret.com.qa/en/</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2265,81 +2265,81 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Men</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://brandsco.qa/</t>
+          <t>https://www.victoriassecret.com.qa/en/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Chantelle</t>
+          <t>VogaCloset</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://chantelle.com/shop/en-qa?popup=popup-user-location&amp;userCountry=US&amp;lang=en</t>
+          <t>https://vogacloset.com/qatar/</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Custom (Next.js)</t>
+          <t>custom/unknown</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://chantelle.com/shop/en-qa?popup=popup-user-location&amp;userCountry=US&amp;lang=en</t>
+          <t>https://web.archive.org/web/20260713004429/https://vogacloset.com/qatar/ar/beauty/haircare/hair-treatments/joico-joico-blonde-life-brilliant-glow-brightening-oil-100ml-gsh-mp-jco1103066.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Coudre</t>
+          <t>Zara Qatar</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://coudre.qa/</t>
+          <t>https://www.zara.com/qa/en/</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2349,39 +2349,39 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>WordPress</t>
+          <t>custom/unknown</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Verified (secondary evidence)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://coudre.qa/</t>
+          <t>https://web.archive.org/web/20260521053824/https://www.zara.com/qa/ar/%D8%A7%D9%94%D9%81%D8%B1%D9%88%D9%84-%D8%A8%D8%AD%D9%8A%D8%A7%D9%83%D8%A9-%D9%83%D8%B1%D9%88%D8%B4%D9%8A%D9%87-p02209489.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Dar Al Qaftan</t>
+          <t>Ace &amp; Zian Women Clothing</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://daralqaftan.qa/</t>
+          <t>https://aceandzianwomenclothing.qa/</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2411,19 +2411,19 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://daralqaftan.qa/collections.json</t>
+          <t>https://aceandzianwomenclothing.qa/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Dart</t>
+          <t>Afraa Boutique</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://dartline.qa/</t>
+          <t>https://afraaboutique.com/</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2453,34 +2453,34 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://dartline.qa/wp-json/wc/store/v1/products/categories</t>
+          <t>https://afraaboutique.com/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Dary</t>
+          <t>Aisope</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://dary.com.qa/</t>
+          <t>https://aisope.qa/</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>shopify</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2495,19 +2495,19 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://dary.com.qa/</t>
+          <t>https://aisope.qa/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Digital Depot (Akasya)</t>
+          <t>Almotahajiba</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://digitaldepot.qa/</t>
+          <t>https://www.almotahajiba.com/</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2522,7 +2522,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2532,24 +2532,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://digitaldepot.qa/</t>
+          <t>https://www.almotahajiba.com/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Doko Fashion Wear</t>
+          <t>Ami Paris</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://dokofashionwear.qa/</t>
+          <t>https://www.amiparis.com/en-qa/</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2574,44 +2574,44 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://dokofashionwear.qa/</t>
+          <t>https://www.amiparis.com/en-qa/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dolce &amp; Gabbana</t>
+          <t>Azul</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.dolcegabbana.com/en-us/</t>
+          <t>https://www.azul.qa/</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Salesforce Commerce Cloud</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2621,19 +2621,19 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.dolcegabbana.com/en-us/</t>
+          <t>https://www.azul.qa/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Dreams</t>
+          <t>Balmain</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.dreams.com.qa/</t>
+          <t>https://balmain.com/en-qa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>odoo</t>
+          <t>shopify</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2658,24 +2658,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://dreams.com.qa/</t>
+          <t>https://balmain.com/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Emvano</t>
+          <t>Brands Outlet</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://emvano.qa/</t>
+          <t>https://brandsoutletglobal.com/</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>custom/unknown</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2705,34 +2705,34 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://emvano.qa/</t>
+          <t>https://brandsoutletglobal.com/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Eupathy</t>
+          <t>Brands Qatar</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://eupathy.qa/</t>
+          <t>https://brandsco.qa/</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Men</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2742,24 +2742,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://eupathy.qa/</t>
+          <t>https://brandsco.qa/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>FAZI</t>
+          <t>Byerley</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://fazi.qa/</t>
+          <t>https://byerley.qa/</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2769,12 +2769,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Men</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2784,24 +2784,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://fazi.qa/</t>
+          <t>https://byerley.qa/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Fetch</t>
+          <t>Chantelle</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://fetch.qa/</t>
+          <t>https://chantelle.com/shop/en-qa?popup=popup-user-location&amp;userCountry=US&amp;lang=en</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2811,17 +2811,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Custom (Next.js)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2831,19 +2831,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://fetch.qa/</t>
+          <t>https://chantelle.com/shop/en-qa?popup=popup-user-location&amp;userCountry=US&amp;lang=en</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FIGS</t>
+          <t>Coudre</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.wearfigs.com/en-QA/</t>
+          <t>https://coudre.qa/</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>shopify</t>
+          <t>WordPress</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2873,24 +2873,24 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.wearfigs.com/en-QA/</t>
+          <t>https://coudre.qa/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Fitwell</t>
+          <t>Dar Al Qaftan</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://fitwell.qa/</t>
+          <t>https://daralqaftan.qa/</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>WooCommerce</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2910,24 +2910,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://fitwell.qa/wp-json/wc/store/v1/products/categories</t>
+          <t>https://daralqaftan.qa/collections.json</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Grizzly</t>
+          <t>Dart</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://grizzly.qa/</t>
+          <t>https://dartline.qa/</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2957,24 +2957,24 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://grizzly.qa/</t>
+          <t>https://dartline.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Hermosa QA</t>
+          <t>Dary</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://hermosa.qa/</t>
+          <t>https://dary.com.qa/</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>shopify</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2999,19 +2999,19 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://hermosa.qa/collections.json</t>
+          <t>https://dary.com.qa/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Instaura Lingerie</t>
+          <t>Digital Depot (Akasya)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://instaura.qa/</t>
+          <t>https://digitaldepot.qa/</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>shopify</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3041,19 +3041,19 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://instaura.qa/</t>
+          <t>https://digitaldepot.qa/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Jaya</t>
+          <t>Doko Fashion Wear</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://jaya-qa.com/</t>
+          <t>https://dokofashionwear.qa/</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>woocommerce</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3083,34 +3083,34 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://jaya-qa.com/</t>
+          <t>https://dokofashionwear.qa/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Lichi</t>
+          <t>Dolce &amp; Gabbana</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://lichi.com/qa/en</t>
+          <t>https://www.dolcegabbana.com/en-us/</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Custom (Next.js)</t>
+          <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3120,24 +3120,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://lichi.com/qa/en</t>
+          <t>https://www.dolcegabbana.com/en-us/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Luisa Spagnoli</t>
+          <t>Dreams</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.luisaspagnoli.com/en/qa</t>
+          <t>https://www.dreams.com.qa/</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -3152,34 +3152,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Salesforce Commerce Cloud</t>
+          <t>odoo</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.luisaspagnoli.com/en/qa</t>
+          <t>https://dreams.com.qa/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Luna Couture</t>
+          <t>Emvano</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://lunacouture.qa/</t>
+          <t>https://emvano.qa/</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>WooCommerce</t>
+          <t>custom/unknown</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3209,34 +3209,34 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://lunacouture.qa/wp-json/wc/store/v1/products/categories</t>
+          <t>https://emvano.qa/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mac Duggal Qatar</t>
+          <t>Eupathy</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://qa.macduggal.com/</t>
+          <t>https://eupathy.qa/</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3246,24 +3246,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://qa.macduggal.com/</t>
+          <t>https://eupathy.qa/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Maje Qatar</t>
+          <t>FAZI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.maje.qa/</t>
+          <t>https://fazi.qa/</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>shopify</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3288,24 +3288,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://maje.qa/</t>
+          <t>https://fazi.qa/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Malika Clothing</t>
+          <t>Fetch</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.malikaclothing.qa/</t>
+          <t>https://fetch.qa/</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Custom/Other</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3330,24 +3330,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.malikaclothing.qa/collections.json</t>
+          <t>https://fetch.qa/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mandala Qatar</t>
+          <t>FIGS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://mandala.qa/</t>
+          <t>https://www.wearfigs.com/en-QA/</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -3357,12 +3357,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>shopify</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3377,24 +3377,24 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://mandala.qa/collections.json</t>
+          <t>https://www.wearfigs.com/en-QA/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mijade QA</t>
+          <t>Fitwell</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://mijade.qa/</t>
+          <t>https://fitwell.qa/</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3419,19 +3419,19 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://mijade.qa/wp-json/wc/store/v1/products/categories</t>
+          <t>https://fitwell.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>My Abaya</t>
+          <t>Grizzly</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://myabaya.qa/</t>
+          <t>https://grizzly.qa/</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>WooCommerce</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3456,39 +3456,39 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://myabaya.qa/</t>
+          <t>https://grizzly.qa/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Nimbus</t>
+          <t>Hermosa QA</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://nimbus.com.qa/</t>
+          <t>https://hermosa.qa/</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>woocommerce</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3503,19 +3503,19 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://nimbus.com.qa/</t>
+          <t>https://hermosa.qa/collections.json</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Nymphaea Abayas</t>
+          <t>Instaura Lingerie</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.nymphaea.qa/</t>
+          <t>https://instaura.qa/</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3530,7 +3530,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>WooCommerce</t>
+          <t>shopify</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3540,24 +3540,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.nymphaea.qa/</t>
+          <t>https://instaura.qa/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Off Pitch</t>
+          <t>Jaya</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.offpitch.qa/en</t>
+          <t>https://jaya-qa.com/</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3567,17 +3567,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Custom (Next.js)</t>
+          <t>woocommerce</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -3587,34 +3587,34 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.offpitch.qa/en</t>
+          <t>https://jaya-qa.com/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Out of the Blue</t>
+          <t>Kham</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://outoftheblue.qa/</t>
+          <t>https://kham.qa/</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>shopify</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3624,39 +3624,39 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://outoftheblue.qa/</t>
+          <t>https://kham.qa/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Peak Qatar</t>
+          <t>KHAT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://peak.qa/ar/</t>
+          <t>https://khat.qa/</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>WooCommerce</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3666,39 +3666,39 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://peak.qa/wp-json/wc/store/v1/products/categories</t>
+          <t>https://khat.qa/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Phati</t>
+          <t>Kickers Qatar</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.phati.qa/</t>
+          <t>https://kickers.qa/</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Unisex</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3708,24 +3708,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.phati.qa/</t>
+          <t>https://kickers.qa/</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Qfit</t>
+          <t>La Perle</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://qfit.qa/</t>
+          <t>https://laperleline.qa/</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>WooCommerce</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3755,19 +3755,19 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://qfit.qa/wp-json/wc/store/v1/products/categories</t>
+          <t>https://laperleline.qa/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Roma Style</t>
+          <t>Laseta Designs</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://roumastyle.qa/</t>
+          <t>https://laseta.qa/</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>WooCommerce</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3792,24 +3792,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://roumastyle.qa/wp-json/wc/store/v1/products/categories</t>
+          <t>https://laseta.qa/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Romano</t>
+          <t>Lichi</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://romano.qa/en</t>
+          <t>https://lichi.com/qa/en</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3834,24 +3834,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+          <t>Verified</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://romano.qa/en</t>
+          <t>https://lichi.com/qa/en</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Rumi Earth</t>
+          <t>LIN</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.rumi.co/?shpxid=85c5c1b5-7bf5-4d5f-b442-15f5e273a0d1</t>
+          <t>https://lin.com.qa/</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3876,24 +3876,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.rumi.co/collections.json</t>
+          <t>https://lin.com.qa/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sadil</t>
+          <t>Louzan Qatar</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://sadil.qa/</t>
+          <t>https://louzanqatar.com/</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3918,66 +3918,66 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://sadil.qa/collections.json</t>
+          <t>https://louzanqatar.com/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sama Store</t>
+          <t>Luisa Spagnoli</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.samastore.qa/</t>
+          <t>https://www.luisaspagnoli.com/en/qa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.samastore.qa/collections.json</t>
+          <t>https://www.luisaspagnoli.com/en/qa</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sandro Qatar</t>
+          <t>Luna Couture</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.sandro.qa/</t>
+          <t>https://lunacouture.qa/</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Custom/Other</t>
+          <t>WooCommerce</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4007,19 +4007,19 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.sandro.qa/</t>
+          <t>https://lunacouture.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Shop Five</t>
+          <t>Mac Duggal Qatar</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.shop5.qa/</t>
+          <t>https://qa.macduggal.com/</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Men</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>shopify</t>
+          <t>Shopify</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4049,19 +4049,19 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.shop5.qa/</t>
+          <t>https://qa.macduggal.com/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Skylink</t>
+          <t>Maje Qatar</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://skylink.qa/</t>
+          <t>https://www.maje.qa/</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>WooCommerce</t>
+          <t>shopify</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4091,19 +4091,19 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://skylink.qa/wp-json/wc/store/v1/products/categories</t>
+          <t>https://maje.qa/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Squatwolf Qatar</t>
+          <t>Malika Clothing</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://squatwolf.com/en-qa</t>
+          <t>https://www.malikaclothing.qa/</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4113,7 +4113,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4133,29 +4133,29 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://squatwolf.com/en-qa</t>
+          <t>https://www.malikaclothing.qa/collections.json</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Swish.qa</t>
+          <t>Mandala Qatar</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://swish.qa/</t>
+          <t>https://mandala.qa/</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Has clothing section</t>
+          <t>Fashion-only</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -4175,19 +4175,19 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://swish.qa/collections.json</t>
+          <t>https://mandala.qa/collections.json</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Tafaul Hub</t>
+          <t>Mijade QA</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://tafaul.com.qa/</t>
+          <t>https://mijade.qa/</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>woocommerce</t>
+          <t>WooCommerce</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4217,19 +4217,19 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://tafaul.com.qa/</t>
+          <t>https://mijade.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>The Jacket Maker</t>
+          <t>My Abaya</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.thejacketmaker.qa/</t>
+          <t>https://myabaya.qa/</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Unisex</t>
+          <t>Women</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -4254,39 +4254,39 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.thejacketmaker.qa/</t>
+          <t>https://myabaya.qa/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Trendy Corner</t>
+          <t>Naseej</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://trendycorner.qa/</t>
+          <t>https://naseej.qa/</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Fashion-only</t>
+          <t>Has clothing section</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Women</t>
+          <t>Men</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Shopify</t>
+          <t>WooCommerce</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4296,24 +4296,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://trendycorner.qa/collections.json</t>
+          <t>https://naseej.qa/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Undiz</t>
+          <t>Naya</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://int.undiz.com/en_QA/home</t>
+          <t>https://naya.qa/</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -4328,7 +4328,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>salesforce-commerce</t>
+          <t>Custom</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4338,54 +4338,1104 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Verified</t>
+          <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://int.undiz.com/en_QA/</t>
+          <t>https://naya.qa/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>Nimbus</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://nimbus.com.qa/</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>woocommerce</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://nimbus.com.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Nymphaea Abayas</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://www.nymphaea.qa/</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>WooCommerce</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://www.nymphaea.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Off Pitch</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://www.offpitch.qa/en</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Custom (Next.js)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://www.offpitch.qa/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Out of the Blue</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://outoftheblue.qa/</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Has clothing section</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://outoftheblue.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Peak Qatar</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://peak.qa/ar/</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Has clothing section</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>WooCommerce</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://peak.qa/wp-json/wc/store/v1/products/categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Phati</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.phati.qa/</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Custom/Other</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://www.phati.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>ProSwimwear Qatar</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.proswimwear.qa/</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://www.proswimwear.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Qfit</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://qfit.qa/</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>WooCommerce</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://qfit.qa/wp-json/wc/store/v1/products/categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Roma Style</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://roumastyle.qa/</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>WooCommerce</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://roumastyle.qa/wp-json/wc/store/v1/products/categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Romano</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://romano.qa/en</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Custom (Next.js)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://romano.qa/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Rumi Earth</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://www.rumi.co/?shpxid=85c5c1b5-7bf5-4d5f-b442-15f5e273a0d1</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://www.rumi.co/collections.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Sadil</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://sadil.qa/</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://sadil.qa/collections.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Sama Store</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://www.samastore.qa/</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Has clothing section</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://www.samastore.qa/collections.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Sandro Qatar</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://www.sandro.qa/</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Custom/Other</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://www.sandro.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Shop Five</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://www.shop5.qa/</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Men</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>shopify</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://www.shop5.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Skylink</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://skylink.qa/</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>WooCommerce</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://skylink.qa/wp-json/wc/store/v1/products/categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Soleil</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://soleil.qa/</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://soleil.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Squatwolf Qatar</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://squatwolf.com/en-qa</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://squatwolf.com/en-qa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Summer Salt</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://summer-salt.qa/</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://summer-salt.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Swish.qa</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://swish.qa/</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Has clothing section</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://swish.qa/collections.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Tafaul Hub</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://tafaul.com.qa/</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>woocommerce</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://tafaul.com.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>The Jacket Maker</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://www.thejacketmaker.qa/</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Custom/Other</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://www.thejacketmaker.qa/</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Trendy Corner</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://trendycorner.qa/</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://trendycorner.qa/collections.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Undiz</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://int.undiz.com/en_QA/home</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>salesforce-commerce</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://int.undiz.com/en_QA/</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>Vanilla Wear</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>https://vanillawear-qa.com/</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Fashion-only</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>https://vanillawear-qa.com/wp-json/wc/store/v1/products/categories</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Voile Fashion</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://voilefashion.com/</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://voilefashion.com/</t>
         </is>
       </c>
     </row>
@@ -4400,7 +5450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4582,22 +5632,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Burberry</t>
+          <t>Bizay</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://www.burberry.com/</t>
+          <t>https://bizay.qa/</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Qatar storefront not verified (bot-wall/weak signal): unresolved: live check 'weak_ecommerce_evidence_custom_platform: product URLs in sit'; secondary evidence insufficient (none of wayback_prod</t>
+          <t>Personalized uniform/printing shop (B2B-leaning)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Timeout retry</t>
         </is>
       </c>
     </row>
@@ -4626,105 +5676,101 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Calvin Klein</t>
+          <t>Colehaan.qa</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://www.calvinklein.qa/</t>
+          <t>colehaan.qa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Qatar storefront not verified (bot-wall/weak signal): unresolved: calvinklein.qa returns HTTP 403 live (not bypassed); one current proof (archived Qatar page 2025-11-22); no Qatar shopping app f</t>
+          <t>shoes/bags/accessories-focused</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Calvin Klein Qatar</t>
+          <t>Culture Circle</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://www.calvinklein.qa/</t>
+          <t>culture-circle.com</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HTTP 403 bot-wall; Qatar storefront not verified</t>
+          <t>sneakers/accessories resale; not a Qatar storefront</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>New discovery attempt</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Carrefour Qatar</t>
+          <t>Customon</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.carrefourqatar.com/</t>
+          <t>customon.com</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Plain fetch returned no catalog; clothing section not verifiable - MANUAL CHECK RECOMMENDED (likely qualifies)</t>
+          <t>non-Qatar print-on-demand site</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Known major</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Colehaan.qa</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>colehaan.qa</t>
-        </is>
-      </c>
+          <t>DeFacto</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>shoes/bags/accessories-focused</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Culture Circle</t>
+          <t>Dohalist</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>culture-circle.com</t>
+          <t>dohalist.com</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sneakers/accessories resale; not a Qatar storefront</t>
+          <t>classifieds</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4736,57 +5782,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Customon</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>customon.com</t>
-        </is>
-      </c>
+          <t>FENDI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>non-Qatar print-on-demand site</t>
+          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>DeFacto</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
+          <t>FOG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>fog.qa</t>
+        </is>
+      </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>printing services</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dohalist</t>
+          <t>Factory Online Shopping</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>dohalist.com</t>
+          <t>factory.qa</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>classifieds</t>
+          <t>textile industry directory</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4798,97 +5844,97 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>FENDI</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
+          <t>Farfetch Qatar</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>https://www.farfetch.com/qa/</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
+          <t>Multi-boutique marketplace (excluded as marketplace/aggregator)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Brand re-check</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>FOG</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>fog.qa</t>
-        </is>
-      </c>
+          <t>Forever 21</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>printing services</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Factory Online Shopping</t>
+          <t>Galeries Lafayette Doha</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>factory.qa</t>
+          <t>https://www.galerieslafayette.qa/</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>textile industry directory</t>
+          <t>Department store; only beauty/perfume product evidence found, clothing not confirmed</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Directory re-check</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Forever 21</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://www.gap.com/</t>
+        </is>
+      </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>Only a Qatar App Store app (Gap Middle East); no Qatar web storefront found</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Brand re-check</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gap</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>https://www.gap.com/</t>
-        </is>
-      </c>
+          <t>Givenchy</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Qatar storefront not verified (bot-wall/weak signal): unresolved: live check 'insufficient_market_signals (score=0.0)'; secondary evidence insufficient (app_store of wayback_product, commoncrawl</t>
+          <t>excluded: no Qatar storefront found (Qatar URL variants, Wayback CDX checked)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -4900,13 +5946,13 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Givenchy</t>
+          <t>Gucci</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found (Qatar URL variants, Wayback CDX checked)</t>
+          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4918,18 +5964,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gucci</t>
+          <t>Hawra Abaya / Perla / Matador / Mnsaj / Abaya Studio</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
+          <t>Saudi-focused stores; no Qatar currency/storefront evidence</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>App Store</t>
         </is>
       </c>
     </row>
@@ -5074,17 +6120,13 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lacoste</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>https://lacoste.com/</t>
-        </is>
-      </c>
+          <t>Levi's</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Qatar storefront not verified (bot-wall/weak signal): unresolved: live check 'blocked_or_challenge_http_403'; secondary evidence not yet collected</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5096,18 +6138,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Levi's</t>
+          <t>Lifestyle / LC Waikiki / DeFacto / Koton / Levi's / Puma / New Balance / Skechers / Uniqlo / Banana Republic / R&amp;B</t>
         </is>
       </c>
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>No Qatar-locale URLs found in Common Crawl (2025-51, 2026-17) and no live Qatar storefront</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Brand re-check</t>
         </is>
       </c>
     </row>
@@ -5142,157 +6184,157 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bot-walled (HTTP 403); fashion/clothing section could not be verified live - MANUAL CHECK RECOMMENDED (likely qualifies)</t>
+          <t>Bot-walled (HTTP 403) and Common Crawl holds only one 403 URL for gcc.luluhypermarket.com/en-qa; no fashion/clothing page evidence found - MANUAL CHECK RECOMMENDED (likely sells clothing)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Known major</t>
+          <t>Brand re-check</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Matching Couple Outfits, Women's Dress, Tankinis, Men's Shirts</t>
+          <t>Maheeb</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dresslily.com</t>
+          <t>https://maheeb.qa/</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>non-Qatar storefront</t>
+          <t>Placeholder/example products</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Timeout retry</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Mayfair - مايفير</t>
+          <t>Mamas &amp; Papas Qatar</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>mayfair.qa</t>
+          <t>https://en.mamasandpapas.qa/</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>perfume store</t>
+          <t>Baby/kids-only</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Common Crawl</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Megapolis</t>
+          <t>Matching Couple Outfits, Women's Dress, Tankinis, Men's Shirts</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://megapolisqatar.com/index.html</t>
+          <t>dresslily.com</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>unresolved: live check 'no_ecommerce_evidence'; secondary evidence not yet collected</t>
+          <t>non-Qatar storefront</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Miu Miu</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
+          <t>Mayfair - مايفير</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>mayfair.qa</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
+          <t>perfume store</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Mothercare Qatar</t>
+          <t>Megapolis</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>mothercare.qa</t>
+          <t>https://megapolisqatar.com/index.html</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>kids/baby-only</t>
+          <t>unresolved: live check 'no_ecommerce_evidence'; secondary evidence not yet collected</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Mumzworld</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>mumzworld.com</t>
-        </is>
-      </c>
+          <t>Miu Miu</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>baby/kids marketplace</t>
+          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Mytheresa</t>
+          <t>Mothercare Qatar</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>mytheresa.qa</t>
+          <t>mothercare.qa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>no Qatar storefront evidence</t>
+          <t>kids/baby-only</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -5304,17 +6346,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NEW YORKER</t>
+          <t>Mumzworld</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>newyorker.de</t>
+          <t>mumzworld.com</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>German site; no Qatar storefront evidence</t>
+          <t>baby/kids marketplace</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -5326,49 +6368,57 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>New Look</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr"/>
+          <t>Mytheresa</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>mytheresa.qa</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>no Qatar storefront evidence</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Old Navy</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr"/>
+          <t>NEW YORKER</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>newyorker.de</t>
+        </is>
+      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>German site; no Qatar storefront evidence</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Prada</t>
+          <t>New Look</t>
         </is>
       </c>
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5380,29 +6430,25 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PrettyLittleThing</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prettylittlething.eu</t>
-        </is>
-      </c>
+          <t>Old Navy</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>no Qatar storefront signal</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Pucci</t>
+          <t>Prada</t>
         </is>
       </c>
       <c r="B50" t="inlineStr"/>
@@ -5420,57 +6466,53 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr"/>
+          <t>PrettyLittleThing</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prettylittlething.eu</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>no Qatar storefront signal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Qarma</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>qarmainspect.com</t>
-        </is>
-      </c>
+          <t>Pucci</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>B2B software</t>
+          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Qatar General Broadcasting and Television Corporation</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>https://qmc.qa/</t>
-        </is>
-      </c>
+          <t>Puma</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>unresolved: live check 'no_ecommerce_evidence'; secondary evidence not yet collected</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5482,17 +6524,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Qatar Kicks</t>
+          <t>Qarma</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>qkicks.qa</t>
+          <t>qarmainspect.com</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sneakers-focused</t>
+          <t>B2B software</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5504,39 +6546,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Qmax Qatar</t>
+          <t>Qatar General Broadcasting and Television Corporation</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>qmax.qa</t>
+          <t>https://qmc.qa/</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>home goods (clothes racks only)</t>
+          <t>unresolved: live check 'no_ecommerce_evidence'; secondary evidence not yet collected</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Qunifromfactory</t>
+          <t>Qatar Kicks</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>quniformfactory.qa</t>
+          <t>qkicks.qa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>textile industry directory</t>
+          <t>sneakers-focused</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5548,115 +6590,119 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R&amp;B Fashion</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr"/>
+          <t>Qmax Qatar</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>qmax.qa</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>home goods (clothes racks only)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>River Island</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr"/>
+          <t>Qunifromfactory</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>quniformfactory.qa</t>
+        </is>
+      </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>textile industry directory</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SSK TRADING WLL</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>sskqatar.com</t>
-        </is>
-      </c>
+          <t>R&amp;B Fashion</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PPE / B2B workwear</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STOREY</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>storey.shop</t>
-        </is>
-      </c>
+          <t>River Island</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>multi-brand marketplace</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Saint Laurent Paris</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr"/>
+          <t>SSK TRADING WLL</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>sskqatar.com</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
+          <t>PPE / B2B workwear</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Shamiya Store</t>
+          <t>STOREY</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>shamiyastore.qa</t>
+          <t>storey.shop</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>kids-only (no adult signal)</t>
+          <t>multi-brand marketplace</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5668,127 +6714,123 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Souqly Qatar</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>souqly.com.qa</t>
-        </is>
-      </c>
+          <t>Saint Laurent Paris</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>multi-vendor marketplace</t>
+          <t>excluded: no Qatar storefront found (Qatar URL variants checked)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Splash</t>
+          <t>Shamiya Store</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://www.splashfashions.com/qa/</t>
+          <t>shamiyastore.qa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Qatar storefront unverified (bot-wall / no Qatar page found)</t>
+          <t>kids-only (no adult signal)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>New discovery attempt</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>StoreCensus</t>
+          <t>Sivvi</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>storecensus.com</t>
+          <t>https://www.sivvi.com/</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>directory (not a store)</t>
+          <t>Only robots.txt in Common Crawl; no Qatar storefront evidence</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Brand re-check</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Styli</t>
+          <t>Souqly Qatar</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://stylishop.com/qa/</t>
+          <t>souqly.com.qa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Qatar storefront not verified (bot-wall/weak signal): unresolved: live check 'blocked_or_challenge_http_403'; secondary evidence not yet collected</t>
+          <t>multi-vendor marketplace</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Tawar Mall</t>
+          <t>Splash</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>tawarmall.net</t>
+          <t>https://www.splashfashions.com/qa/</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>mall directory / aggregator</t>
+          <t>No Qatar-locale URLs in Common Crawl (2025-51, 2026-17); bot-walled</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Brand re-check</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>The Fashion Square</t>
+          <t>StoreCensus</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>the-fashion-square.com</t>
+          <t>storecensus.com</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US storefront; no Qatar evidence</t>
+          <t>directory (not a store)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5800,17 +6842,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>The Perfume Factory</t>
+          <t>Tawar Mall</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>theperfumefactory.qa</t>
+          <t>tawarmall.net</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>textile industry directory</t>
+          <t>mall directory / aggregator</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5822,17 +6864,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Toda</t>
+          <t>The Fashion Square</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>toda.qa</t>
+          <t>the-fashion-square.com</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>no clothing evidence</t>
+          <t>US storefront; no Qatar evidence</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5844,47 +6886,51 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Tommy Hilfiger</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr"/>
+          <t>The Perfume Factory</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>theperfumefactory.qa</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>textile industry directory</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Tommy Hilfiger Qatar</t>
+          <t>Toda</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://qa.tommy.com/</t>
+          <t>toda.qa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Not reachable / no Qatar storefront verified</t>
+          <t>no clothing evidence</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>New discovery attempt</t>
+          <t>Qatar directory / candidates</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Under Armour</t>
+          <t>Tommy Hilfiger</t>
         </is>
       </c>
       <c r="B73" t="inlineStr"/>
@@ -5902,101 +6948,97 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Uniqlo</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr"/>
+          <t>Tommy Hilfiger Qatar</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://qa.tommy.com/</t>
+        </is>
+      </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
+          <t>No Qatar-locale URLs found in Common Crawl; not reachable</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Brand re-check</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>benrahim.qa</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>benrahim.qa</t>
-        </is>
-      </c>
+          <t>Under Armour</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>unclear (trading company)</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>embassy of Singapore in Qatar</t>
+          <t>Under Armour (underarmour.ae)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.mfa.gov.sg/</t>
+          <t>https://www.underarmour.ae/</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>unresolved: live check 'insufficient_ecommerce_evidence: 8 price strings'; secondary evidence not yet collected</t>
+          <t>UAE storefront only (2,802 CC URLs are .ae); no Qatar storefront</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Reference universe</t>
+          <t>Brand re-check</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>getit.qa</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>getit.qa</t>
-        </is>
-      </c>
+          <t>Uniqlo</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>general store; clothing not confirmed</t>
+          <t>excluded: no Qatar storefront found after extended search (path-pattern Wayback product probes (qa, en-qa, qa-en, qa/en, qa/ar, en_qa, qa_en, qatar, shop./qa./.com.qa host variants), hreflang/selector</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>kiddostore.qa</t>
+          <t>benrahim.qa</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>kiddostore.qa</t>
+          <t>benrahim.qa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>kids-only</t>
+          <t>unclear (trading company)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6008,39 +7050,39 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>localbazar.qa</t>
+          <t>embassy of Singapore in Qatar</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>localbazar.qa</t>
+          <t>https://www.mfa.gov.sg/</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>multi-vendor marketplace</t>
+          <t>unresolved: live check 'insufficient_ecommerce_evidence: 8 price strings'; secondary evidence not yet collected</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Qatar directory / candidates</t>
+          <t>Reference universe</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>nitted.qa</t>
+          <t>getit.qa</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nitted.qa</t>
+          <t>getit.qa</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>custom T-shirt printing service</t>
+          <t>general store; clothing not confirmed</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6052,17 +7094,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>safetywares</t>
+          <t>kiddostore.qa</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>safetywares.qa</t>
+          <t>kiddostore.qa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PPE / B2B workwear</t>
+          <t>kids-only</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6074,17 +7116,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>signinn.qa</t>
+          <t>localbazar.qa</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>signinn.qa</t>
+          <t>localbazar.qa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>waterproofing/HVAC firm</t>
+          <t>multi-vendor marketplace</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6096,17 +7138,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>theiconic.qa</t>
+          <t>nitted.qa</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>theiconic.qa</t>
+          <t>nitted.qa</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Australian site; no Qatar storefront</t>
+          <t>custom T-shirt printing service</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6118,17 +7160,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tinyWorld</t>
+          <t>safetywares</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>tinyworld.qa</t>
+          <t>safetywares.qa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>baby/kids-only</t>
+          <t>PPE / B2B workwear</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6140,17 +7182,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>verno</t>
+          <t>signinn.qa</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>verno.qa</t>
+          <t>signinn.qa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>no clothing evidence</t>
+          <t>waterproofing/HVAC firm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6162,20 +7204,86 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>theiconic.qa</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>theiconic.qa</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Australian site; no Qatar storefront</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Qatar directory / candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>tinyWorld</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>tinyworld.qa</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>baby/kids-only</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Qatar directory / candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>verno</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>verno.qa</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>no clothing evidence</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Qatar directory / candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
           <t>دكان</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B89" t="inlineStr">
         <is>
           <t>dokanonline.qa</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>unverified general store, fashion not confirmed</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>Qatar directory / candidates</t>
         </is>
@@ -6192,7 +7300,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -6219,7 +7327,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>118</t>
         </is>
       </c>
     </row>
@@ -6231,7 +7339,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>{'Fashion-only': 72, 'Has clothing section': 21}</t>
+          <t>{'Fashion-only': 90, 'Has clothing section': 28}</t>
         </is>
       </c>
     </row>
@@ -6243,7 +7351,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>{'Unisex': 51, 'Women': 39, 'Men': 3}</t>
+          <t>{'Unisex': 62, 'Women': 51, 'Men': 5}</t>
         </is>
       </c>
     </row>
@@ -6255,7 +7363,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -6267,7 +7375,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -6310,46 +7418,58 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Pass 2 (new discovery)</t>
+          <t>Pass 3 (deep discovery)</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>~220 GCC/global fashion brand Qatar-storefront URL guesses (Alshaya/Apparel Group/Landmark/Azadea/Chalhoub/MAF/Al-Futtaim style brands), 52 extra fashion-named hosts from DB candidates, Qatar App Store search (country=qa), Wayback CDX and StoreCensus attempts (returned nothing usable). New stores kept only if a Qatar-locale storefront responded.</t>
+          <t>Common Crawl cluster-index scan of the entire .qa TLD for 4 crawls (CC-MAIN-2025-38, 2025-51, 2026-08, 2026-17): 4,073 unique .qa hosts; 1,106 not already in the DB were probed. The CC index API host (index.commoncrawl.org) was down and Wayback wildcard CDX queries require authorization (403) / were offline, so cluster.idx range reads on data.commoncrawl.org were used instead. 1,370 first-pass fetch timeouts/errors were retried with longer timeouts (this recovered local abaya stores). Qatar App Store: 30+ fashion queries (EN/AR) -&gt; 1,096 seller hosts probed; kept only those with QAR currency/Qatar delivery signals. Brand re-check via Common Crawl URL lookups (Namshi, Ounass, American Eagle, Carrefour, PrettyLittleThing) plus stored/archived evidence. Salla/Zid/Shopify host-list enumeration by path was NOT possible (no usable host-list source); only .qa hosts and App Store sellers were covered.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Exclusions</t>
+          <t>Pass 2 (new discovery)</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Kids/baby-only, shoes/bags/jewelry/perfume/eyewear-only, B2B uniforms/PPE, marketplaces/classifieds/directories, closed stores, non-Qatar sites, service/print shops.</t>
+          <t>~220 GCC/global fashion brand Qatar-storefront URL guesses (Alshaya/Apparel Group/Landmark/Azadea/Chalhoub/MAF/Al-Futtaim style brands), 52 extra fashion-named hosts from DB candidates, Qatar App Store search (country=qa), Wayback CDX and StoreCensus attempts (returned nothing usable). New stores kept only if a Qatar-locale storefront responded.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>Exclusions</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Random sample of 50 reviewed: 3 errors (6%) - below 8% threshold. Errors: Next Qatar type (fixed to Has clothing section), Skylink (clothing not confirmed, thin page), Roma Style (borderline abaya/home items).</t>
+          <t>Kids/baby-only, shoes/bags/jewelry/perfume/eyewear-only, B2B uniforms/PPE, marketplaces/classifieds/directories, closed stores, non-Qatar sites, service/print shops.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Pass 1: random 50 sample, 3 errors (6%). Pass 3: all 25 additions manually reviewed against homepage nav/title; 0 clear errors, 11 rows labelled Unverified because the Qatar purchase path could not be confirmed on static/JS pages.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
           <t>Limitations</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Bot-walled majors (Zara group, Mango, Lulu, Carrefour, Next) rely on prior secondary evidence or are flagged. Gender for fetch-failed sites is partly inferred from names/DB category. Size tier is a heuristic (known brand / platform / catalog size). No Common Crawl bulk pass and Wayback CDX was unavailable; discovery recall for small local Shopify/Salla abaya stores is limited. Salla/Zid stores were not separately enumerated.</t>
         </is>

--- a/markets/fashion/Qatar_Fashion_Stores.xlsx
+++ b/markets/fashion/Qatar_Fashion_Stores.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fashion Stores" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Excluded" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage &amp; Method" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed - platform subdomain" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -7248,7 +7249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7423,7 +7424,6 @@
         </is>
       </c>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -7433,6 +7433,94 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>Removed 1 rows from Fashion Stores (now 117); each is listed in the Excluded sheet with source "Deliverable cleanup (fashion-stores package)". Website values normalised to clean storefront URLs (5 changed). Counts above (total, type, gender, platform, size tier, verification status) reflect the cleaned list; any by-source/by-channel/signal-origin/QA breakdowns are as at the original run (pre-cleanup).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Root-domain cleanup</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Rows before</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Kept as-is</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Replaced with root domain</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Removed (no own domain / duplicate of root)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Rows after</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Store Name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Old URL</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Reason</t>
         </is>
       </c>
     </row>

--- a/markets/fashion/Qatar_Fashion_Stores.xlsx
+++ b/markets/fashion/Qatar_Fashion_Stores.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,6 +31,9 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -58,12 +61,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,17 +435,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -453,32 +462,47 @@
           <t>Website</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Website Pages Count</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Count Method</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Count Date</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Size Tier (best-effort)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Verification Status</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Evidence URL</t>
         </is>
@@ -495,32 +519,45 @@
           <t>https://ar-qa.aivi.com/</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="n">
+        <v>16312869</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>https://ar-qa.aivi.com/</t>
         </is>
@@ -537,32 +574,45 @@
           <t>https://www.adidas.qa/en/</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="n">
+        <v>2496</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>https://www.adidas.qa/en/</t>
         </is>
@@ -579,32 +629,45 @@
           <t>https://qa.alnasser.net/</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="n">
+        <v>13825</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>https://qa.alnasser.net/</t>
         </is>
@@ -621,32 +684,43 @@
           <t>https://www.americaneagle.com.qa/</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20250322231222/https://www.americaneagle.com.qa/ar/american-eagle/shop-women/bottoms/shorts/</t>
         </is>
@@ -663,32 +737,45 @@
           <t>https://www.balenciaga.com/en-qa</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>sitemap (QA pages only)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Qatar-locale storefront (en-qa, QAR)</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>https://www.balenciaga.com/en-qa</t>
         </is>
@@ -705,32 +792,43 @@
           <t>https://www.bershka.com/qa/</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260613215835/https://www.bershka.com/qa/ar/%D8%A7%D9%84%D9%86%D8%B3%D8%A7%D8%A1/%D9%85%D9%84%D8%A7%D8%A8%D8%B3/%D9%81%D8%B3%D8%A7%D8%AA%D9%8A%D9%86-n3802.html</t>
         </is>
@@ -747,32 +845,45 @@
           <t>https://qa.burberry.com/</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="n">
+        <v>3875</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>Qatar-locale storefront (qa.burberry.com); no QAR on homepage</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>https://qa.burberry.com/</t>
         </is>
@@ -789,32 +900,43 @@
           <t>https://www.calvinklein.qa/</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>Known major retailer – manually accepted (403 bot-wall, not bypassed)</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251122044217/https://www.calvinklein.qa/ar/kids-black-friday-early.html</t>
         </is>
@@ -831,32 +953,43 @@
           <t>https://www.carrefourqatar.com/mafqat/en/</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Not available (unreachable (ReadTimeout: HTTPConnectionPool(host='www.carrefourqatar.com', port=80): Read timed out. (rea))</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>https://www.carrefourqatar.com/mafqat/en/men-t-shirt/mens-tshirt-ss-plain/p/981282</t>
         </is>
@@ -873,32 +1006,45 @@
           <t>https://www.centrepointstores.com/qa/en/</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="4" t="n">
+        <v>65605</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20220612014351/https://www.centrepointstores.com/qa/en/Women/Clothing/Dresses/SPLASH-Ruched-Printed-Midi-Shift-Dress-with-Short-Sleeves/p/1020622</t>
         </is>
@@ -915,32 +1061,45 @@
           <t>https://www.chloe.com/qa/</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="4" t="n">
+        <v>2348</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>sitemap (QA pages only)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>https://www.chloe.com/qa/</t>
         </is>
@@ -957,32 +1116,45 @@
           <t>https://decathlon.qa/</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="4" t="n">
+        <v>4035</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>https://decathlon.qa/</t>
         </is>
@@ -999,32 +1171,45 @@
           <t>https://www.desigual.com/en_QA/</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="4" t="n">
+        <v>6220</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>https://www.desigual.com/en_QA/</t>
         </is>
@@ -1041,32 +1226,43 @@
           <t>https://www.footlocker.qa/en/</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>https://www.footlocker.qa/en/</t>
         </is>
@@ -1083,32 +1279,45 @@
           <t>https://giordano.qa/</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="4" t="n">
+        <v>391</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>https://giordano.qa/collections.json</t>
         </is>
@@ -1125,32 +1334,45 @@
           <t>https://www.gymshark.qa/</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="4" t="n">
+        <v>8092</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>https://www.gymshark.qa/</t>
         </is>
@@ -1167,32 +1389,45 @@
           <t>https://www.lacoste.qa/</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="4" t="n">
+        <v>2560</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Known major retailer – Qatar storefront (lacoste.qa, QAR)</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>https://www.lacoste.qa/</t>
         </is>
@@ -1209,32 +1444,43 @@
           <t>https://shop.mango.com/qa/en/</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 429 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260617064834/https://shop.mango.com/qa/ar/c/%D8%A7%D9%84%D8%A7%D8%B7%D9%81%D8%A7%D9%84/%D8%A7%D9%88%D9%84%D8%A7%D8%AF-%D8%B5%D8%BA%D8%A7%D8%B1/%D8%A8%D9%84%D8%A7%D9%8A%D8%B2/9b255289</t>
         </is>
@@ -1251,32 +1497,45 @@
           <t>https://www.marksandspencer.qa/en/fashion</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="4" t="n">
+        <v>7705</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>https://www.marksandspencerme.com/en-qa/</t>
         </is>
@@ -1293,32 +1552,43 @@
           <t>https://www.massimodutti.com/qa/</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20261006232223/https://www.massimodutti.com/qa/100-raffia-midsized-tote-bag-l06922605</t>
         </is>
@@ -1335,32 +1605,45 @@
           <t>https://www.matalanme.com/qa_ar</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="4" t="n">
+        <v>21617</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>sitemap (QA pages only)</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>https://www.matalanme.com/qa_ar/</t>
         </is>
@@ -1377,32 +1660,43 @@
           <t>https://www.maxfashion.com/qa/en/</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Known major retailer – manually accepted</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20250706160300/https://www.maxfashion.com/qa/en/</t>
         </is>
@@ -1419,32 +1713,43 @@
           <t>https://www.muji.qa/en/</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>https://www.muji.qa/en/</t>
         </is>
@@ -1461,32 +1766,43 @@
           <t>https://www.namshi.com/qatar-en/</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Not available (unreachable (ReadTimeout: HTTPConnectionPool(host='www.namshi.com', port=80): Read timed out. (read timeou))</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>https://www.namshi.com/qatar-en/buy-2xtremz-textured-dress-with-short-sleeves-and-pockets/Z3B43CABEDCDDD73D9CA8Z/p/</t>
         </is>
@@ -1503,32 +1819,43 @@
           <t>https://www.next.qa/</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>https://www.next.qa/Next-QA-AR-Products-1.xml.gz</t>
         </is>
@@ -1545,32 +1872,45 @@
           <t>https://www.nike.qa/en/</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="4" t="n">
+        <v>24496</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>https://www.nike.qa/en/home/</t>
         </is>
@@ -1587,32 +1927,45 @@
           <t>https://www.ounass.qa/</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="4" t="n">
+        <v>342593</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>https://www.ounass.qa/shop-emporio-armani-eagle-patch-zip-hoodie-for-kids-00438af14935_4067.html</t>
         </is>
@@ -1629,32 +1982,43 @@
           <t>https://www.oysho.com/qa/</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260712062634/https://www.oysho.com/qa/2-square-piping-hair-claws-l33180414</t>
         </is>
@@ -1671,32 +2035,45 @@
           <t>https://www.prettylittlething.qa/</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="4" t="n">
+        <v>44119</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Custom (Magento)</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Known major retailer – manually accepted (Cloudflare-protected, not bypassed)</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>https://www.prettylittlething.qa/animal-printed-onion-skin-bandeau-maxi-dress.html</t>
         </is>
@@ -1713,32 +2090,43 @@
           <t>https://www.pullandbear.com/qa/</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260712213550/https://www.pullandbear.com/qa/ar/%D8%A7%D9%84%D8%B1%D8%AC%D8%A7%D9%84/%D9%85%D9%84%D8%A7%D8%A8%D8%B3/anime-n7253?celement=1030378186</t>
         </is>
@@ -1755,32 +2143,45 @@
           <t>https://replayjeans.qa/</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>https://replayjeans.qa/</t>
         </is>
@@ -1797,32 +2198,45 @@
           <t>https://www.rivafashion.com/en-qa/</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="4" t="n">
+        <v>74598</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>magento</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>https://www.rivafashion.com/en-qa/</t>
         </is>
@@ -1839,32 +2253,45 @@
           <t>https://salams.com/</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="4" t="n">
+        <v>17968</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Magento</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>https://salams.com/</t>
         </is>
@@ -1881,32 +2308,43 @@
           <t>https://ar.shein.com/</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Not available (unreachable (ConnectionError: HTTPConnectionPool(host='www.ar.shein.com', port=80): Max retries exceeded with ))</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Known major retailer – manually accepted</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>https://ar.shein.com/</t>
         </is>
@@ -1923,32 +2361,43 @@
           <t>https://www.stradivarius.com/qa/</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260712091550/https://www.stradivarius.com/qa/d09-super-highwaist-skinny-jeans-l01450741</t>
         </is>
@@ -1965,32 +2414,45 @@
           <t>https://stylishop.com/qa/en</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="4" t="n">
+        <v>247204</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Qatar-locale storefront (/qa/en); bot-light page, no QAR on homepage</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>https://stylishop.com/qa/en</t>
         </is>
@@ -2007,32 +2469,45 @@
           <t>https://suitsupply.com/en-qa/</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="4" t="n">
+        <v>4932</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>sitemap (QA pages only)</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>https://suitsupply.com/en-qa/</t>
         </is>
@@ -2049,32 +2524,45 @@
           <t>https://en-qa.sssports.com/</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="4" t="n">
+        <v>119876</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>https://en-qa.sssports.com/</t>
         </is>
@@ -2091,32 +2579,45 @@
           <t>https://www.tedbaker.qa/</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="4" t="n">
+        <v>2463</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>https://www.tedbaker.qa/collections.json</t>
         </is>
@@ -2133,32 +2634,45 @@
           <t>https://www.shoptriumph.qa/</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="4" t="n">
+        <v>1306</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>https://www.shoptriumph.qa/</t>
         </is>
@@ -2175,32 +2689,45 @@
           <t>https://www.valentino.com/en-qa/</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="4" t="n">
+        <v>2355</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>sitemap (QA pages only)</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>https://www.valentino.com/en-qa/</t>
         </is>
@@ -2217,32 +2744,45 @@
           <t>https://www.victoriassecret.com.qa/en/</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="4" t="n">
+        <v>20135</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>https://www.victoriassecret.com.qa/en/</t>
         </is>
@@ -2259,32 +2799,45 @@
           <t>https://vogacloset.com/qatar/</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="4" t="n">
+        <v>738413</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260713004429/https://vogacloset.com/qatar/ar/beauty/haircare/hair-treatments/joico-joico-blonde-life-brilliant-glow-brightening-oil-100ml-gsh-mp-jco1103066.html</t>
         </is>
@@ -2301,32 +2854,43 @@
           <t>https://www.zara.com/qa/en/</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260521053824/https://www.zara.com/qa/ar/%D8%A7%D9%94%D9%81%D8%B1%D9%88%D9%84-%D8%A8%D8%AD%D9%8A%D8%A7%D9%83%D8%A9-%D9%83%D8%B1%D9%88%D8%B4%D9%8A%D9%87-p02209489.html</t>
         </is>
@@ -2343,32 +2907,45 @@
           <t>https://aceandzianwomenclothing.qa/</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>https://aceandzianwomenclothing.qa/</t>
         </is>
@@ -2385,32 +2962,45 @@
           <t>https://afraaboutique.com/</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>https://afraaboutique.com/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -2427,32 +3017,45 @@
           <t>https://aisope.qa/</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="4" t="n">
+        <v>454</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>https://aisope.qa/</t>
         </is>
@@ -2469,32 +3072,45 @@
           <t>https://www.almotahajiba.com/</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="4" t="n">
+        <v>713</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>https://www.almotahajiba.com/</t>
         </is>
@@ -2511,32 +3127,45 @@
           <t>https://www.amiparis.com/en-qa/</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="4" t="n">
+        <v>198368</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>https://www.amiparis.com/en-qa/</t>
         </is>
@@ -2553,32 +3182,45 @@
           <t>https://www.azul.qa/</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>https://www.azul.qa/</t>
         </is>
@@ -2595,32 +3237,45 @@
           <t>https://balmain.com/en-qa</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="4" t="n">
+        <v>240077</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>https://balmain.com/</t>
         </is>
@@ -2637,32 +3292,45 @@
           <t>https://brandsoutletglobal.com/</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="4" t="n">
+        <v>10630</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>https://brandsoutletglobal.com/</t>
         </is>
@@ -2679,32 +3347,45 @@
           <t>https://brandsco.qa/</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="4" t="n">
+        <v>386</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>https://brandsco.qa/</t>
         </is>
@@ -2721,32 +3402,45 @@
           <t>https://byerley.qa/</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="4" t="n">
+        <v>215</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>https://byerley.qa/</t>
         </is>
@@ -2763,32 +3457,45 @@
           <t>https://chantelle.com/shop/en-qa</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="4" t="n">
+        <v>99798</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>https://chantelle.com/shop/en-qa?popup=popup-user-location&amp;userCountry=US&amp;lang=en</t>
         </is>
@@ -2805,32 +3512,45 @@
           <t>https://coudre.qa/</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="4" t="n">
+        <v>484</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>https://coudre.qa/</t>
         </is>
@@ -2847,32 +3567,45 @@
           <t>https://daralqaftan.qa/</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>https://daralqaftan.qa/collections.json</t>
         </is>
@@ -2889,32 +3622,45 @@
           <t>https://dartline.qa/</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>https://dartline.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -2931,32 +3677,45 @@
           <t>https://dary.com.qa/</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="4" t="n">
+        <v>135</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>https://dary.com.qa/</t>
         </is>
@@ -2973,32 +3732,45 @@
           <t>https://digitaldepot.qa/</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="4" t="n">
+        <v>311</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>https://digitaldepot.qa/</t>
         </is>
@@ -3015,32 +3787,45 @@
           <t>https://dokofashionwear.qa/</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="4" t="n">
+        <v>3099</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>https://dokofashionwear.qa/</t>
         </is>
@@ -3057,32 +3842,45 @@
           <t>https://www.dolcegabbana.com/en-qa/</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="4" t="n">
+        <v>12897</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>sitemap (QA pages only)</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>https://www.dolcegabbana.com/en-us/</t>
         </is>
@@ -3099,32 +3897,45 @@
           <t>https://www.dreams.com.qa/</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="4" t="n">
+        <v>165</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>odoo</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="J64" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>https://dreams.com.qa/</t>
         </is>
@@ -3141,32 +3952,45 @@
           <t>https://emvano.qa/</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="4" t="n">
+        <v>76156</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>https://emvano.qa/</t>
         </is>
@@ -3183,32 +4007,45 @@
           <t>https://eupathy.qa/</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>https://eupathy.qa/</t>
         </is>
@@ -3225,32 +4062,45 @@
           <t>https://fazi.qa/</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="J67" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>https://fazi.qa/</t>
         </is>
@@ -3267,32 +4117,45 @@
           <t>https://fetch.qa/</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="4" t="n">
+        <v>958</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="J68" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>https://fetch.qa/</t>
         </is>
@@ -3309,32 +4172,45 @@
           <t>https://www.wearfigs.com/en-QA/</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="4" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="J69" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>https://www.wearfigs.com/en-QA/</t>
         </is>
@@ -3351,32 +4227,45 @@
           <t>https://fitwell.qa/</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="4" t="n">
+        <v>825</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>https://fitwell.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -3393,32 +4282,45 @@
           <t>https://grizzly.qa/</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="4" t="n">
+        <v>75</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>https://grizzly.qa/</t>
         </is>
@@ -3435,32 +4337,45 @@
           <t>https://hermosa.qa/</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="4" t="n">
+        <v>2233</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="G72" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="I72" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="J72" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>https://hermosa.qa/collections.json</t>
         </is>
@@ -3477,32 +4392,45 @@
           <t>https://instaura.qa/</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="4" t="n">
+        <v>317</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="G73" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="I73" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="J73" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>https://instaura.qa/</t>
         </is>
@@ -3519,32 +4447,45 @@
           <t>https://jaya-qa.com/</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>shop-page total</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="G74" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>woocommerce</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="I74" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="J74" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>https://jaya-qa.com/</t>
         </is>
@@ -3561,32 +4502,45 @@
           <t>https://kham.qa/</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="4" t="n">
+        <v>262</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>https://kham.qa/</t>
         </is>
@@ -3603,32 +4557,45 @@
           <t>https://khat.qa/</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="4" t="n">
+        <v>632</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="J76" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>https://khat.qa/</t>
         </is>
@@ -3645,32 +4612,45 @@
           <t>https://kickers.qa/</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="4" t="n">
+        <v>431</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>https://kickers.qa/</t>
         </is>
@@ -3687,32 +4667,45 @@
           <t>https://laperleline.qa/</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="G78" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="I78" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="J78" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>https://laperleline.qa/</t>
         </is>
@@ -3729,32 +4722,45 @@
           <t>https://laseta.qa/</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="4" t="n">
+        <v>192</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="G79" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="I79" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="J79" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>https://laseta.qa/</t>
         </is>
@@ -3771,32 +4777,45 @@
           <t>https://lichi.com/qa/en</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="4" t="n">
+        <v>2408</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>sitemap (QA pages only)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="G80" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="I80" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="J80" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>https://lichi.com/qa/en</t>
         </is>
@@ -3813,32 +4832,45 @@
           <t>https://lin.com.qa/</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="4" t="n">
+        <v>405</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="G81" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>https://lin.com.qa/</t>
         </is>
@@ -3855,32 +4887,45 @@
           <t>https://louzanqatar.com/</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="4" t="n">
+        <v>278</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="G82" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>https://louzanqatar.com/</t>
         </is>
@@ -3897,32 +4942,45 @@
           <t>https://www.luisaspagnoli.com/en/qa</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="4" t="n">
+        <v>19032</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="G83" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>https://www.luisaspagnoli.com/en/qa</t>
         </is>
@@ -3939,32 +4997,45 @@
           <t>https://lunacouture.qa/</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="4" t="n">
+        <v>379</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>platform product count</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="G84" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="I84" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>https://lunacouture.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -3981,32 +5052,45 @@
           <t>https://qa.macduggal.com/</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="4" t="n">
+        <v>3725</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="J85" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>https://qa.macduggal.com/</t>
         </is>
@@ -4023,32 +5107,45 @@
           <t>https://www.maje.qa/</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C86" s="4" t="n">
+        <v>1337</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D86" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="J86" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>https://maje.qa/</t>
         </is>
@@ -4065,32 +5162,45 @@
           <t>https://www.malikaclothing.qa/</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="4" t="n">
+        <v>803</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>https://www.malikaclothing.qa/collections.json</t>
         </is>
@@ -4107,32 +5217,45 @@
           <t>https://mandala.qa/</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C88" s="4" t="n">
+        <v>79</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>https://mandala.qa/collections.json</t>
         </is>
@@ -4149,32 +5272,45 @@
           <t>https://mijade.qa/</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C89" s="4" t="n">
+        <v>375</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="G89" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="I89" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="J89" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>https://mijade.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -4191,32 +5327,45 @@
           <t>https://myabaya.qa/</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C90" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="G90" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="I90" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="J90" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>https://myabaya.qa/</t>
         </is>
@@ -4233,32 +5382,45 @@
           <t>https://naseej.qa/</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C91" s="4" t="n">
+        <v>326</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="G91" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="I91" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="J91" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>https://naseej.qa/</t>
         </is>
@@ -4275,32 +5437,45 @@
           <t>https://naya.qa/</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
+      <c r="C92" s="4" t="n">
+        <v>129</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
+      <c r="G92" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>https://naya.qa/</t>
         </is>
@@ -4317,32 +5492,45 @@
           <t>https://nimbus.com.qa/</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C93" s="4" t="n">
+        <v>634</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="G93" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>woocommerce</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="I93" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="J93" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>https://nimbus.com.qa/</t>
         </is>
@@ -4359,32 +5547,45 @@
           <t>https://www.nymphaea.qa/</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C94" s="4" t="n">
+        <v>119</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
+      <c r="G94" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="I94" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>https://www.nymphaea.qa/</t>
         </is>
@@ -4401,32 +5602,45 @@
           <t>https://www.offpitch.qa/en</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C95" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr">
+      <c r="G95" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="I95" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="J95" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>https://www.offpitch.qa/en</t>
         </is>
@@ -4443,32 +5657,45 @@
           <t>https://outoftheblue.qa/</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="4" t="n">
+        <v>3036</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="G96" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="I96" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="J96" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>https://outoftheblue.qa/</t>
         </is>
@@ -4485,32 +5712,45 @@
           <t>https://peak.qa/ar/</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="4" t="n">
+        <v>2558</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="G97" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="I97" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="J97" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>https://peak.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -4527,32 +5767,45 @@
           <t>https://www.phati.qa/</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="4" t="n">
+        <v>259</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="G98" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="I98" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>https://www.phati.qa/</t>
         </is>
@@ -4569,32 +5822,45 @@
           <t>https://www.proswimwear.qa/</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="4" t="n">
+        <v>6143</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
+      <c r="G99" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="I99" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="J99" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>https://www.proswimwear.qa/</t>
         </is>
@@ -4611,32 +5877,45 @@
           <t>https://qfit.qa/</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C100" s="4" t="n">
+        <v>442</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="G100" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="I100" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="J100" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>https://qfit.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -4653,32 +5932,45 @@
           <t>https://roumastyle.qa/</t>
         </is>
       </c>
-      <c r="C101" t="inlineStr">
+      <c r="C101" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
+      <c r="G101" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="I101" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="J101" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>https://roumastyle.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -4695,32 +5987,45 @@
           <t>https://romano.qa/en</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C102" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>shop-page total</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="G102" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="I102" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="J102" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>https://romano.qa/en</t>
         </is>
@@ -4737,32 +6042,45 @@
           <t>https://www.rumi.co/</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C103" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>sitemap (QA pages only)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>https://www.rumi.co/collections.json</t>
         </is>
@@ -4779,32 +6097,45 @@
           <t>https://sadil.qa/</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C104" s="4" t="n">
+        <v>87</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>https://sadil.qa/collections.json</t>
         </is>
@@ -4821,32 +6152,45 @@
           <t>https://www.samastore.qa/</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C105" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="G105" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>https://www.samastore.qa/collections.json</t>
         </is>
@@ -4863,32 +6207,45 @@
           <t>https://www.sandro.qa/</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C106" s="4" t="n">
+        <v>1554</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>https://www.sandro.qa/</t>
         </is>
@@ -4905,32 +6262,43 @@
           <t>https://www.shop5.qa/</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C107" s="4" t="n"/>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Not available (unreachable (ConnectionError: HTTPConnectionPool(host='www.shop5.qa', port=80): Max retries exceeded with url:))</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="E107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>https://www.shop5.qa/</t>
         </is>
@@ -4947,32 +6315,45 @@
           <t>https://skylink.qa/</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C108" s="4" t="n">
+        <v>156</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="G108" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="I108" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="J108" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>https://skylink.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -4989,32 +6370,45 @@
           <t>https://soleil.qa/</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C109" s="4" t="n">
+        <v>514</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>https://soleil.qa/</t>
         </is>
@@ -5031,32 +6425,45 @@
           <t>https://squatwolf.com/en-qa</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C110" s="4" t="n">
+        <v>3222</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>sitemap (QA pages only)</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>https://squatwolf.com/en-qa</t>
         </is>
@@ -5073,32 +6480,45 @@
           <t>https://summer-salt.qa/</t>
         </is>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C111" s="4" t="n">
+        <v>272</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>https://summer-salt.qa/</t>
         </is>
@@ -5115,32 +6535,45 @@
           <t>https://swish.qa/</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C112" s="4" t="n">
+        <v>12141</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="G112" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="I112" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="J112" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>https://swish.qa/collections.json</t>
         </is>
@@ -5157,32 +6590,45 @@
           <t>https://tafaul.com.qa/</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
+      <c r="G113" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>woocommerce</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>https://tafaul.com.qa/</t>
         </is>
@@ -5199,32 +6645,45 @@
           <t>https://www.thejacketmaker.qa/</t>
         </is>
       </c>
-      <c r="C114" t="inlineStr">
+      <c r="C114" s="4" t="n">
+        <v>1702</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr">
+      <c r="G114" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="E114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="I114" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="J114" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>https://www.thejacketmaker.qa/</t>
         </is>
@@ -5241,32 +6700,45 @@
           <t>https://trendycorner.qa/</t>
         </is>
       </c>
-      <c r="C115" t="inlineStr">
+      <c r="C115" s="4" t="n">
+        <v>74</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
+      <c r="G115" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="I115" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="J115" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>https://trendycorner.qa/collections.json</t>
         </is>
@@ -5283,32 +6755,43 @@
           <t>https://int.undiz.com/en_QA/</t>
         </is>
       </c>
-      <c r="C116" t="inlineStr">
+      <c r="C116" s="4" t="n"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Not available (blocked by site: HTTP 403 on robots.txt; not bypassed)</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>salesforce-commerce</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="I116" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="J116" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t>https://int.undiz.com/en_QA/</t>
         </is>
@@ -5325,32 +6808,45 @@
           <t>https://vanillawear-qa.com/</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C117" s="4" t="n">
+        <v>76</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="G117" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="I117" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="J117" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>https://vanillawear-qa.com/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -5367,32 +6863,45 @@
           <t>https://voilefashion.com/</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C118" s="4" t="n">
+        <v>9533</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="E118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>https://voilefashion.com/</t>
         </is>
@@ -7249,7 +8758,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:C46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -7424,6 +8933,7 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
@@ -7436,6 +8946,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
@@ -7493,7 +9004,188 @@
         <v>117</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Page count</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Rows counted (of 117)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Counted by method</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>platform product count</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>shop-page total</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Size distribution (pages per site)</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1-50</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>51-200</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>201-1,000</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>1,001-5,000</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>5,001-20,000</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20,001-100,000</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>&gt;100,000</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0 (market segment empty)</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" ht="95" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A46:C46"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/markets/fashion/Qatar_Fashion_Stores.xlsx
+++ b/markets/fashion/Qatar_Fashion_Stores.xlsx
@@ -738,11 +738,11 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0</v>
+        <v>22704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sitemap (QA pages only)</t>
+          <t>sitemap (partial: 27 of 28 sitemap files read)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>342593</v>
+        <v>387593</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>15</v>
+        <v>652</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sitemap</t>
+          <t>sitemap (partial: 83 of 84 sitemap files read)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>sitemap</t>
+          <t>sitemap (partial: 14 of 15 sitemap files read)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>75</v>
+        <v>143</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -5658,7 +5658,7 @@
         </is>
       </c>
       <c r="C96" s="4" t="n">
-        <v>3036</v>
+        <v>3997</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>sitemap</t>
+          <t>sitemap (partial: 53 of 57 sitemap files read)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -5987,12 +5987,10 @@
           <t>https://romano.qa/en</t>
         </is>
       </c>
-      <c r="C102" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C102" s="4" t="n"/>
       <c r="D102" t="inlineStr">
         <is>
-          <t>shop-page total</t>
+          <t>Not available (no sitemap; shop-page total reported 0)</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6042,12 +6040,10 @@
           <t>https://www.rumi.co/</t>
         </is>
       </c>
-      <c r="C103" s="4" t="n">
-        <v>0</v>
-      </c>
+      <c r="C103" s="4" t="n"/>
       <c r="D103" t="inlineStr">
         <is>
-          <t>sitemap (QA pages only)</t>
+          <t>Not available (no QA pages in sitemap)</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6208,7 +6204,7 @@
         </is>
       </c>
       <c r="C106" s="4" t="n">
-        <v>1554</v>
+        <v>1829</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9018,7 +9014,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29">
@@ -9040,7 +9036,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31">
@@ -9070,115 +9066,115 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>sitemap (partial: some child sitemaps unreadable)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>Not available</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="B35" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Size distribution (pages per site)</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Rows</t>
         </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1-50</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>51-200</t>
+          <t>1-50</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>201-1,000</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1,001-5,000</t>
+          <t>201-1,000</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>5,001-20,000</t>
+          <t>1,001-5,000</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>20,001-100,000</t>
+          <t>5,001-20,000</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>&gt;100,000</t>
+          <t>20,001-100,000</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0 (market segment empty)</t>
+          <t>&gt;100,000</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" ht="95" customHeight="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" ht="150" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank.</t>
+          <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank. Child sitemaps that failed are retried up to 4 times (5s/15s/45s/120s); if some still fail the row reads 'sitemap (partial: N of M sitemap files read)' and the count is a lower bound. If the sitemap has country segments but none for the listed market, the whole site is counted when a default storefront exists ('sitemap (whole site, no market segment)', which includes other-country URLs), otherwise the row is Not available.</t>
         </is>
       </c>
     </row>

--- a/markets/fashion/Qatar_Fashion_Stores.xlsx
+++ b/markets/fashion/Qatar_Fashion_Stores.xlsx
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>99798</v>
+        <v>99774</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -4998,11 +4998,11 @@
         </is>
       </c>
       <c r="C84" s="4" t="n">
-        <v>379</v>
+        <v>1902</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>platform product count</t>
+          <t>sitemap</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>sitemap (partial: 53 of 57 sitemap files read)</t>
+          <t>sitemap</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6258,10 +6258,12 @@
           <t>https://www.shop5.qa/</t>
         </is>
       </c>
-      <c r="C107" s="4" t="n"/>
+      <c r="C107" s="4" t="n">
+        <v>3903</v>
+      </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Not available (unreachable (ConnectionError: HTTPConnectionPool(host='www.shop5.qa', port=80): Max retries exceeded with url:))</t>
+          <t>sitemap</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -6312,11 +6314,11 @@
         </is>
       </c>
       <c r="C108" s="4" t="n">
-        <v>156</v>
+        <v>116</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>archive</t>
+          <t>sitemap</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8754,7 +8756,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C46"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -9014,7 +9016,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29">
@@ -9036,7 +9038,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31">
@@ -9046,13 +9048,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>platform product count</t>
+          <t>shop-page total</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -9062,117 +9064,107 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>shop-page total</t>
+          <t>sitemap (partial: some child sitemaps unreadable)</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sitemap (partial: some child sitemaps unreadable)</t>
+          <t>Not available</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>20</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Size distribution (pages per site)</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>Size distribution (pages per site)</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Rows</t>
-        </is>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>1-50</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1-50</t>
+          <t>51-200</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>51-200</t>
+          <t>201-1,000</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>201-1,000</t>
+          <t>1,001-5,000</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1,001-5,000</t>
+          <t>5,001-20,000</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>5,001-20,000</t>
+          <t>20,001-100,000</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>20,001-100,000</t>
+          <t>&gt;100,000</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>&gt;100,000</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="46" ht="150" customHeight="1">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45" ht="150" customHeight="1">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank. Child sitemaps that failed are retried up to 4 times (5s/15s/45s/120s); if some still fail the row reads 'sitemap (partial: N of M sitemap files read)' and the count is a lower bound. If the sitemap has country segments but none for the listed market, the whole site is counted when a default storefront exists ('sitemap (whole site, no market segment)', which includes other-country URLs), otherwise the row is Not available.</t>
         </is>
@@ -9180,7 +9172,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A46:C46"/>
+    <mergeCell ref="A45:C45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/markets/fashion/Qatar_Fashion_Stores.xlsx
+++ b/markets/fashion/Qatar_Fashion_Stores.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K118"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -6905,6 +6905,388 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Luxury Shopping in Qatar</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://51east.com/</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>27603</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Has clothing section</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Women, Men</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Magento</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Large</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>https://51east.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Haneenalsaify</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>https://www.haneenalsaify.com/</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>767</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>https://www.haneenalsaify.com/products/soft-fit-cotton-hijab</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Lusso Moda</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>https://lusso-moda.com/</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>537</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Shopify</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>https://lusso-moda.com/products/first-light</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>sheikhastyleboutique</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>https://www.sheikhastyle.com/</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>88</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Wix</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>https://www.sheikhastyle.com/perfumes</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Shop Lamees</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>https://www.shoplamees.com/</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Not available (sitemap present but yielded no countable URLs; no sitemap/shop total/platform count and no archive captures)</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Salla</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>https://www.shoplamees.com/product/abaya-aneqa-dantel</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ThreeL</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>https://threel.qa/</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>31</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Unisex</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Zid</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>https://threel.qa/products/</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Trendy</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>https://trendyqatar.com/</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>253</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Fashion-only</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Women</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Ecwid</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Small</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Verified – StoreLeads gap check</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://trendyqatar.com/products/search</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6916,7 +7298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -8742,6 +9124,644 @@
       <c r="D90" t="inlineStr">
         <is>
           <t>Deliverable cleanup (fashion-stores package)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Al Hamim</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://www.alhamim.qa/</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>شركة أمانة لتجارة العسل</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://amanah.qa/</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Blue Lynx Online</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://bluelynxonline.com/</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Dahhas</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://dahhas.com/</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Family Qatar</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://familysupermarket.qa/</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Fnac Qatar</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://fnac.qa/</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>FSAHI</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://fsahi.com/</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Gait</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://gait.com.qa/</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Halaly All You Need</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>https://www.halalys.com/</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Harmony Organic Matcha Tea</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>https://www.harmonymatchatea.com/</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>IBN RUSHD PHARMACY</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>https://www.ibnrushdpharmacy.com/</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>لافيلو تريدنغ</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>https://la-filo.com/</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>LACOSTE Online Boutique</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>https://www.lacoste.qa/</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>halafik</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>https://lakhwiya.com/</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>THE LAST BATCH COFFEE ROASTERS</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>https://lastbatch.online/</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>LULEA JEWELRY</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>https://luleajewelryqa.com/</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Maawoon Home Shop</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>https://maawoon.com/</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>متجر قطر</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>https://matgarqatar.com/</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Panda Hypermarket</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>https://panda.qa/</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Qatar Vet Center</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>https://www.qvcpetshop.com/</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>RARE</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>https://rarepharmcy.com/</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Reef Perfumes</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>https://sa.reefperfumes.com/</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>الملكي</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>https://royalnaturalhoney.com/</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Intertec Group W.L.L.</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>https://shopintertec.com/</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Silverlow Pharma</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>https://silverglow.qa/</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Skill Mount Trading</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>https://skilltechqatar.com/</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>The Football Autograph</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>https://thefootballautograph.com/</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Voltaat</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>https://www.voltaat.com/</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>We Sell Everything</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>https://wse.com.qa/</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>no clothing signal (added by StoreLeads gap fill)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill</t>
         </is>
       </c>
     </row>
@@ -8756,7 +9776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C45"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8783,7 +9803,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>124</t>
         </is>
       </c>
     </row>
@@ -8795,7 +9815,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>{'Fashion-only': 90, 'Has clothing section': 27}</t>
+          <t>{'Fashion-only': 96, 'Has clothing section': 28}</t>
         </is>
       </c>
     </row>
@@ -8807,7 +9827,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>{'Unisex': 61, 'Women': 51, 'Men': 5}</t>
+          <t>{'Unisex': 62, 'Women': 56, 'Men': 5, 'Women, Men': 1}</t>
         </is>
       </c>
     </row>
@@ -9002,89 +10022,100 @@
         <v>117</v>
       </c>
     </row>
+    <row r="24"/>
+    <row r="25"/>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Page count</t>
+          <t>StoreLeads gap fill</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rows counted (of 117)</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>98</v>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>StoreLeads gap fill of the Qatar directory (see directory workbook, sheet 'Research Coverage')</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Gap stores added to the directory</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
-        <is>
-          <t>Counted by method</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>Rows</t>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Gap stores added to the fashion list</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>sitemap</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>86</v>
+          <t>Gap stores not fashion (listed in Excluded)</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>archive</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>shop-page total</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-    </row>
+          <t>Fashion rules</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Adult clothing (women, men, unisex) as a fashion-only store or a clothing section; abaya/thobe/modest wear, lingerie and sportswear count; kids-only and shoes/bags/accessories-only do not. Classified from homepage nav/meta and product pages (EN+AR keywords), reviewed manually.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>sitemap (partial: some child sitemaps unreadable)</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>3</v>
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Page count</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Not available</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>19</v>
-      </c>
-    </row>
+          <t>Rows counted (of 124)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Size distribution (pages per site)</t>
+          <t>Counted by method</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
@@ -9096,75 +10127,162 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1-50</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>11</v>
+          <t>sitemap</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>51-200</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>14</v>
+          <t>archive</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>201-1,000</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>24</v>
+          <t>shop-page total</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1,001-5,000</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>22</v>
+          <t>sitemap (partial: some child sitemaps unreadable)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>Not available</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Size distribution (pages per site)</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1-50</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>51-200</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>201-1,000</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1,001-5,000</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>5,001-20,000</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
         <is>
           <t>20,001-100,000</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>&gt;100,000</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" ht="150" customHeight="1">
-      <c r="A45" s="2" t="inlineStr">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="150" customHeight="1">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank. Child sitemaps that failed are retried up to 4 times (5s/15s/45s/120s); if some still fail the row reads 'sitemap (partial: N of M sitemap files read)' and the count is a lower bound. If the sitemap has country segments but none for the listed market, the whole site is counted when a default storefront exists ('sitemap (whole site, no market segment)', which includes other-country URLs), otherwise the row is Not available.</t>
         </is>
@@ -9172,7 +10290,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A52:C52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/markets/fashion/Qatar_Fashion_Stores.xlsx
+++ b/markets/fashion/Qatar_Fashion_Stores.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:O125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -443,12 +443,16 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="34" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="40" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,32 +481,52 @@
           <t>Count Date</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Organic Traffic (QA, Semrush)</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Organic Keywords (QA)</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Traffic Check Date</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Traffic Note</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Size Tier (best-effort)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Verification Status</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Evidence URL</t>
         </is>
@@ -532,32 +556,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" t="n">
+        <v>77</v>
+      </c>
+      <c r="G2" t="n">
+        <v>324</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>https://ar-qa.aivi.com/</t>
         </is>
@@ -587,32 +622,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" t="n">
+        <v>322</v>
+      </c>
+      <c r="G3" t="n">
+        <v>240</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>https://www.adidas.qa/en/</t>
         </is>
@@ -642,32 +688,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" t="n">
+        <v>4127</v>
+      </c>
+      <c r="G4" t="n">
+        <v>500</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>https://qa.alnasser.net/</t>
         </is>
@@ -695,32 +752,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" t="n">
+        <v>5100</v>
+      </c>
+      <c r="G5" t="n">
+        <v>917</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20250322231222/https://www.americaneagle.com.qa/ar/american-eagle/shop-women/bottoms/shorts/</t>
         </is>
@@ -750,32 +818,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" t="n">
+        <v>3058</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2201</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Qatar-locale storefront (en-qa, QAR)</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>https://www.balenciaga.com/en-qa</t>
         </is>
@@ -803,32 +882,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" t="n">
+        <v>8077</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3533</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260613215835/https://www.bershka.com/qa/ar/%D8%A7%D9%84%D9%86%D8%B3%D8%A7%D8%A1/%D9%85%D9%84%D8%A7%D8%A8%D8%B3/%D9%81%D8%B3%D8%A7%D8%AA%D9%8A%D9%86-n3802.html</t>
         </is>
@@ -860,30 +950,45 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Qatar-locale storefront (qa.burberry.com); no QAR on homepage</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>https://qa.burberry.com/</t>
         </is>
@@ -911,32 +1016,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" t="n">
+        <v>6603</v>
+      </c>
+      <c r="G9" t="n">
+        <v>846</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Known major retailer – manually accepted (403 bot-wall, not bypassed)</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20251122044217/https://www.calvinklein.qa/ar/kids-black-friday-early.html</t>
         </is>
@@ -964,32 +1080,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="n">
+        <v>171039</v>
+      </c>
+      <c r="G10" t="n">
+        <v>61872</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>https://www.carrefourqatar.com/mafqat/en/men-t-shirt/mens-tshirt-ss-plain/p/981282</t>
         </is>
@@ -1019,32 +1146,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" t="n">
+        <v>103669</v>
+      </c>
+      <c r="G11" t="n">
+        <v>27639</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20220612014351/https://www.centrepointstores.com/qa/en/Women/Clothing/Dresses/SPLASH-Ruched-Printed-Midi-Shift-Dress-with-Short-Sleeves/p/1020622</t>
         </is>
@@ -1074,32 +1212,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" t="n">
+        <v>1151</v>
+      </c>
+      <c r="G12" t="n">
+        <v>257</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>https://www.chloe.com/qa/</t>
         </is>
@@ -1129,32 +1278,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" t="n">
+        <v>30522</v>
+      </c>
+      <c r="G13" t="n">
+        <v>4213</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="N13" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>https://decathlon.qa/</t>
         </is>
@@ -1184,32 +1344,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" t="n">
+        <v>524</v>
+      </c>
+      <c r="G14" t="n">
+        <v>108</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>https://www.desigual.com/en_QA/</t>
         </is>
@@ -1237,32 +1408,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" t="n">
+        <v>13953</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3211</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>https://www.footlocker.qa/en/</t>
         </is>
@@ -1294,30 +1476,40 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>https://giordano.qa/collections.json</t>
         </is>
@@ -1347,32 +1539,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>1126</v>
+      </c>
+      <c r="G17" t="n">
+        <v>401</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>https://www.gymshark.qa/</t>
         </is>
@@ -1402,32 +1605,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" t="n">
+        <v>3737</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1009</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>Known major retailer – Qatar storefront (lacoste.qa, QAR)</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>https://www.lacoste.qa/</t>
         </is>
@@ -1455,32 +1669,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" t="n">
+        <v>13727</v>
+      </c>
+      <c r="G19" t="n">
+        <v>2125</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260617064834/https://shop.mango.com/qa/ar/c/%D8%A7%D9%84%D8%A7%D8%B7%D9%81%D8%A7%D9%84/%D8%A7%D9%88%D9%84%D8%A7%D8%AF-%D8%B5%D8%BA%D8%A7%D8%B1/%D8%A8%D9%84%D8%A7%D9%8A%D8%B2/9b255289</t>
         </is>
@@ -1510,32 +1735,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" t="n">
+        <v>7313</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1061</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>https://www.marksandspencerme.com/en-qa/</t>
         </is>
@@ -1563,32 +1799,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>6541</v>
+      </c>
+      <c r="G21" t="n">
+        <v>481</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20261006232223/https://www.massimodutti.com/qa/100-raffia-midsized-tote-bag-l06922605</t>
         </is>
@@ -1618,32 +1865,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" t="n">
+        <v>4234</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1743</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>https://www.matalanme.com/qa_ar/</t>
         </is>
@@ -1671,32 +1929,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" t="n">
+        <v>28949</v>
+      </c>
+      <c r="G23" t="n">
+        <v>7074</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Known major retailer – manually accepted</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20250706160300/https://www.maxfashion.com/qa/en/</t>
         </is>
@@ -1724,32 +1993,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" t="n">
+        <v>2589</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1034</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>https://www.muji.qa/en/</t>
         </is>
@@ -1777,32 +2057,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" t="n">
+        <v>12794</v>
+      </c>
+      <c r="G25" t="n">
+        <v>15195</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>https://www.namshi.com/qatar-en/buy-2xtremz-textured-dress-with-short-sleeves-and-pockets/Z3B43CABEDCDDD73D9CA8Z/p/</t>
         </is>
@@ -1830,32 +2121,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>45019</v>
+      </c>
+      <c r="G26" t="n">
+        <v>10382</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>https://www.next.qa/Next-QA-AR-Products-1.xml.gz</t>
         </is>
@@ -1885,32 +2187,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" t="n">
+        <v>24033</v>
+      </c>
+      <c r="G27" t="n">
+        <v>4908</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>https://www.nike.qa/en/home/</t>
         </is>
@@ -1940,32 +2253,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" t="n">
+        <v>31943</v>
+      </c>
+      <c r="G28" t="n">
+        <v>24337</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>https://www.ounass.qa/shop-emporio-armani-eagle-patch-zip-hoodie-for-kids-00438af14935_4067.html</t>
         </is>
@@ -1993,32 +2317,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" t="n">
+        <v>4451</v>
+      </c>
+      <c r="G29" t="n">
+        <v>828</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260712062634/https://www.oysho.com/qa/2-square-piping-hair-claws-l33180414</t>
         </is>
@@ -2050,30 +2385,45 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>Custom (Magento)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>Known major retailer – manually accepted (Cloudflare-protected, not bypassed)</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>https://www.prettylittlething.qa/animal-printed-onion-skin-bandeau-maxi-dress.html</t>
         </is>
@@ -2101,32 +2451,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" t="n">
+        <v>6734</v>
+      </c>
+      <c r="G31" t="n">
+        <v>657</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260712213550/https://www.pullandbear.com/qa/ar/%D8%A7%D9%84%D8%B1%D8%AC%D8%A7%D9%84/%D9%85%D9%84%D8%A7%D8%A8%D8%B3/anime-n7253?celement=1030378186</t>
         </is>
@@ -2156,32 +2517,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" t="n">
+        <v>29</v>
+      </c>
+      <c r="G32" t="n">
+        <v>61</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>https://replayjeans.qa/</t>
         </is>
@@ -2211,32 +2583,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" t="n">
+        <v>3875</v>
+      </c>
+      <c r="G33" t="n">
+        <v>962</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>magento</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>https://www.rivafashion.com/en-qa/</t>
         </is>
@@ -2266,32 +2649,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" t="n">
+        <v>9430</v>
+      </c>
+      <c r="G34" t="n">
+        <v>2422</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>Magento</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>https://salams.com/</t>
         </is>
@@ -2319,32 +2713,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" t="n">
+        <v>17313</v>
+      </c>
+      <c r="G35" t="n">
+        <v>243</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>Known major retailer – manually accepted</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>https://ar.shein.com/</t>
         </is>
@@ -2372,32 +2777,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" t="n">
+        <v>5405</v>
+      </c>
+      <c r="G36" t="n">
+        <v>678</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260712091550/https://www.stradivarius.com/qa/d09-super-highwaist-skinny-jeans-l01450741</t>
         </is>
@@ -2427,32 +2843,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>187</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1882</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>Qatar-locale storefront (/qa/en); bot-light page, no QAR on homepage</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>https://stylishop.com/qa/en</t>
         </is>
@@ -2482,32 +2909,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>308</v>
+      </c>
+      <c r="G38" t="n">
+        <v>156</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="K38" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
+      <c r="M38" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
+      <c r="N38" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>https://suitsupply.com/en-qa/</t>
         </is>
@@ -2537,32 +2975,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" t="n">
+        <v>23773</v>
+      </c>
+      <c r="G39" t="n">
+        <v>6117</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="K39" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>https://en-qa.sssports.com/</t>
         </is>
@@ -2592,32 +3041,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" t="n">
+        <v>1134</v>
+      </c>
+      <c r="G40" t="n">
+        <v>496</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="M40" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr">
+      <c r="N40" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>https://www.tedbaker.qa/collections.json</t>
         </is>
@@ -2647,32 +3107,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" t="n">
+        <v>718</v>
+      </c>
+      <c r="G41" t="n">
+        <v>124</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>https://www.shoptriumph.qa/</t>
         </is>
@@ -2702,32 +3173,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" t="n">
+        <v>2624</v>
+      </c>
+      <c r="G42" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>https://www.valentino.com/en-qa/</t>
         </is>
@@ -2757,32 +3239,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" t="n">
+        <v>12782</v>
+      </c>
+      <c r="G43" t="n">
+        <v>2864</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>https://www.victoriassecret.com.qa/en/</t>
         </is>
@@ -2812,32 +3305,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" t="n">
+        <v>4002</v>
+      </c>
+      <c r="G44" t="n">
+        <v>2515</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260713004429/https://vogacloset.com/qatar/ar/beauty/haircare/hair-treatments/joico-joico-blonde-life-brilliant-glow-brightening-oil-100ml-gsh-mp-jco1103066.html</t>
         </is>
@@ -2865,32 +3369,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" t="n">
+        <v>42730</v>
+      </c>
+      <c r="G45" t="n">
+        <v>4943</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>Verified (secondary evidence)</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>https://web.archive.org/web/20260521053824/https://www.zara.com/qa/ar/%D8%A7%D9%94%D9%81%D8%B1%D9%88%D9%84-%D8%A8%D8%AD%D9%8A%D8%A7%D9%83%D8%A9-%D9%83%D8%B1%D9%88%D8%B4%D9%8A%D9%87-p02209489.html</t>
         </is>
@@ -2922,30 +3437,40 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>https://aceandzianwomenclothing.qa/</t>
         </is>
@@ -2977,30 +3502,40 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>https://afraaboutique.com/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -3032,30 +3567,40 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>https://aisope.qa/</t>
         </is>
@@ -3085,32 +3630,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" t="n">
+        <v>854</v>
+      </c>
+      <c r="G49" t="n">
+        <v>134</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>https://www.almotahajiba.com/</t>
         </is>
@@ -3140,32 +3696,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" t="n">
+        <v>438</v>
+      </c>
+      <c r="G50" t="n">
+        <v>41</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>https://www.amiparis.com/en-qa/</t>
         </is>
@@ -3197,30 +3764,40 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>https://www.azul.qa/</t>
         </is>
@@ -3250,32 +3827,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" t="n">
+        <v>1172</v>
+      </c>
+      <c r="G52" t="n">
+        <v>156</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>https://balmain.com/</t>
         </is>
@@ -3305,32 +3893,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" t="n">
+        <v>1</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>https://brandsoutletglobal.com/</t>
         </is>
@@ -3362,30 +3961,40 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>https://brandsco.qa/</t>
         </is>
@@ -3417,30 +4026,40 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>https://byerley.qa/</t>
         </is>
@@ -3470,32 +4089,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" t="n">
+        <v>40</v>
+      </c>
+      <c r="G56" t="n">
+        <v>22</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>https://chantelle.com/shop/en-qa?popup=popup-user-location&amp;userCountry=US&amp;lang=en</t>
         </is>
@@ -3527,30 +4157,40 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>WordPress</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>https://coudre.qa/</t>
         </is>
@@ -3582,30 +4222,40 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>https://daralqaftan.qa/collections.json</t>
         </is>
@@ -3637,30 +4287,40 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>https://dartline.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -3692,30 +4352,40 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>https://dary.com.qa/</t>
         </is>
@@ -3747,30 +4417,40 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>https://digitaldepot.qa/</t>
         </is>
@@ -3800,32 +4480,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" t="n">
+        <v>26</v>
+      </c>
+      <c r="G62" t="n">
+        <v>337</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>https://dokofashionwear.qa/</t>
         </is>
@@ -3855,32 +4546,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" t="n">
+        <v>3932</v>
+      </c>
+      <c r="G63" t="n">
+        <v>2957</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>https://www.dolcegabbana.com/en-us/</t>
         </is>
@@ -3912,30 +4614,40 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>odoo</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>https://dreams.com.qa/</t>
         </is>
@@ -3965,32 +4677,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" t="n">
+        <v>206</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>custom/unknown</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>https://emvano.qa/</t>
         </is>
@@ -4022,30 +4745,40 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>https://eupathy.qa/</t>
         </is>
@@ -4077,30 +4810,40 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>https://fazi.qa/</t>
         </is>
@@ -4130,32 +4873,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" t="n">
+        <v>3</v>
+      </c>
+      <c r="G68" t="n">
+        <v>38</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>https://fetch.qa/</t>
         </is>
@@ -4185,32 +4939,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" t="n">
+        <v>43</v>
+      </c>
+      <c r="G69" t="n">
+        <v>27</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>https://www.wearfigs.com/en-QA/</t>
         </is>
@@ -4240,32 +5005,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" t="n">
+        <v>167</v>
+      </c>
+      <c r="G70" t="n">
+        <v>29</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>https://fitwell.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -4297,30 +5073,40 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="O71" t="inlineStr">
         <is>
           <t>https://grizzly.qa/</t>
         </is>
@@ -4350,32 +5136,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" t="n">
+        <v>66</v>
+      </c>
+      <c r="G72" t="n">
+        <v>25</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
+      <c r="L72" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="M72" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J72" t="inlineStr">
+      <c r="N72" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr">
+      <c r="O72" t="inlineStr">
         <is>
           <t>https://hermosa.qa/collections.json</t>
         </is>
@@ -4407,30 +5204,40 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="K73" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="L73" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="M73" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J73" t="inlineStr">
+      <c r="N73" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr">
+      <c r="O73" t="inlineStr">
         <is>
           <t>https://instaura.qa/</t>
         </is>
@@ -4462,30 +5269,40 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="K74" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H74" t="inlineStr">
+      <c r="L74" t="inlineStr">
         <is>
           <t>woocommerce</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
+      <c r="M74" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J74" t="inlineStr">
+      <c r="N74" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
+      <c r="O74" t="inlineStr">
         <is>
           <t>https://jaya-qa.com/</t>
         </is>
@@ -4517,30 +5334,40 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="L75" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="M75" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>https://kham.qa/</t>
         </is>
@@ -4570,32 +5397,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="n">
+        <v>14</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="L76" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I76" t="inlineStr">
+      <c r="M76" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="N76" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>https://khat.qa/</t>
         </is>
@@ -4627,30 +5465,40 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="L77" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="M77" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>https://kickers.qa/</t>
         </is>
@@ -4682,30 +5530,40 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="K78" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
+      <c r="L78" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
+      <c r="M78" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J78" t="inlineStr">
+      <c r="N78" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr">
+      <c r="O78" t="inlineStr">
         <is>
           <t>https://laperleline.qa/</t>
         </is>
@@ -4737,30 +5595,40 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="K79" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
+      <c r="L79" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="M79" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
+      <c r="N79" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr">
+      <c r="O79" t="inlineStr">
         <is>
           <t>https://laseta.qa/</t>
         </is>
@@ -4790,32 +5658,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" t="n">
+        <v>778</v>
+      </c>
+      <c r="G80" t="n">
+        <v>84</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
+      <c r="L80" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="I80" t="inlineStr">
+      <c r="M80" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J80" t="inlineStr">
+      <c r="N80" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
+      <c r="O80" t="inlineStr">
         <is>
           <t>https://lichi.com/qa/en</t>
         </is>
@@ -4847,30 +5726,40 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="K81" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="L81" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
+      <c r="M81" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J81" t="inlineStr">
+      <c r="N81" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr">
+      <c r="O81" t="inlineStr">
         <is>
           <t>https://lin.com.qa/</t>
         </is>
@@ -4902,30 +5791,40 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="K82" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
+      <c r="L82" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
+      <c r="M82" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="N82" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr">
+      <c r="O82" t="inlineStr">
         <is>
           <t>https://louzanqatar.com/</t>
         </is>
@@ -4955,32 +5854,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" t="n">
+        <v>192</v>
+      </c>
+      <c r="G83" t="n">
+        <v>16</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>Salesforce Commerce Cloud</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J83" t="inlineStr">
+      <c r="N83" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="O83" t="inlineStr">
         <is>
           <t>https://www.luisaspagnoli.com/en/qa</t>
         </is>
@@ -5012,30 +5922,45 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="L84" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
+      <c r="M84" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J84" t="inlineStr">
+      <c r="N84" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr">
+      <c r="O84" t="inlineStr">
         <is>
           <t>https://lunacouture.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -5065,32 +5990,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" t="n">
+        <v>10</v>
+      </c>
+      <c r="G85" t="n">
+        <v>25</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="L85" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="M85" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr">
+      <c r="O85" t="inlineStr">
         <is>
           <t>https://qa.macduggal.com/</t>
         </is>
@@ -5120,32 +6056,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" t="n">
+        <v>592</v>
+      </c>
+      <c r="G86" t="n">
+        <v>216</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="K86" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="L86" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="M86" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr">
+      <c r="O86" t="inlineStr">
         <is>
           <t>https://maje.qa/</t>
         </is>
@@ -5175,32 +6122,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" t="n">
+        <v>60</v>
+      </c>
+      <c r="G87" t="n">
+        <v>124</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="L87" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="M87" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr">
+      <c r="O87" t="inlineStr">
         <is>
           <t>https://www.malikaclothing.qa/collections.json</t>
         </is>
@@ -5232,30 +6190,40 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="K88" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="L88" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="M88" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>https://mandala.qa/collections.json</t>
         </is>
@@ -5287,30 +6255,40 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="K89" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="L89" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="M89" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="N89" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="O89" t="inlineStr">
         <is>
           <t>https://mijade.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -5342,30 +6320,40 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="K90" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
+      <c r="L90" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
+      <c r="M90" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
+      <c r="N90" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr">
+      <c r="O90" t="inlineStr">
         <is>
           <t>https://myabaya.qa/</t>
         </is>
@@ -5397,30 +6385,40 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="K91" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="L91" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
+      <c r="M91" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J91" t="inlineStr">
+      <c r="N91" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr">
+      <c r="O91" t="inlineStr">
         <is>
           <t>https://naseej.qa/</t>
         </is>
@@ -5452,30 +6450,40 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J92" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>https://naya.qa/</t>
         </is>
@@ -5505,32 +6513,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>4</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="K93" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
+      <c r="L93" t="inlineStr">
         <is>
           <t>woocommerce</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
+      <c r="M93" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
+      <c r="N93" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr">
+      <c r="O93" t="inlineStr">
         <is>
           <t>https://nimbus.com.qa/</t>
         </is>
@@ -5562,30 +6581,40 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
+      <c r="L94" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
+      <c r="M94" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr">
+      <c r="O94" t="inlineStr">
         <is>
           <t>https://www.nymphaea.qa/</t>
         </is>
@@ -5617,30 +6646,40 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="K95" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
+      <c r="L95" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
+      <c r="M95" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J95" t="inlineStr">
+      <c r="N95" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr">
+      <c r="O95" t="inlineStr">
         <is>
           <t>https://www.offpitch.qa/en</t>
         </is>
@@ -5670,32 +6709,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" t="n">
+        <v>533</v>
+      </c>
+      <c r="G96" t="n">
+        <v>49</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="K96" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
+      <c r="L96" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
+      <c r="M96" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr">
+      <c r="N96" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>https://outoftheblue.qa/</t>
         </is>
@@ -5725,32 +6775,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" t="n">
+        <v>89</v>
+      </c>
+      <c r="G97" t="n">
+        <v>62</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="K97" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
+      <c r="L97" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
+      <c r="M97" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J97" t="inlineStr">
+      <c r="N97" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr">
+      <c r="O97" t="inlineStr">
         <is>
           <t>https://peak.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -5782,30 +6843,40 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J98" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr">
+      <c r="O98" t="inlineStr">
         <is>
           <t>https://www.phati.qa/</t>
         </is>
@@ -5835,32 +6906,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>48</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="K99" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
+      <c r="L99" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="M99" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J99" t="inlineStr">
+      <c r="N99" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr">
+      <c r="O99" t="inlineStr">
         <is>
           <t>https://www.proswimwear.qa/</t>
         </is>
@@ -5892,30 +6974,40 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="K100" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
+      <c r="L100" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
+      <c r="M100" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J100" t="inlineStr">
+      <c r="N100" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr">
+      <c r="O100" t="inlineStr">
         <is>
           <t>https://qfit.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -5947,30 +7039,40 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
+      <c r="L101" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
+      <c r="M101" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J101" t="inlineStr">
+      <c r="N101" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="O101" t="inlineStr">
         <is>
           <t>https://roumastyle.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -5998,32 +7100,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" t="n">
+        <v>53</v>
+      </c>
+      <c r="G102" t="n">
+        <v>9</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="K102" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="L102" t="inlineStr">
         <is>
           <t>Custom (Next.js)</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="M102" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="N102" t="inlineStr">
         <is>
           <t>Unverified candidate – weak Qatar signal (fashion-classified)</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="O102" t="inlineStr">
         <is>
           <t>https://romano.qa/en</t>
         </is>
@@ -6053,30 +7166,45 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="N103" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="O103" t="inlineStr">
         <is>
           <t>https://www.rumi.co/collections.json</t>
         </is>
@@ -6108,30 +7236,40 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
+      <c r="L104" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="M104" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="N104" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="O104" t="inlineStr">
         <is>
           <t>https://sadil.qa/collections.json</t>
         </is>
@@ -6163,30 +7301,40 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="L105" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="M105" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="N105" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="O105" t="inlineStr">
         <is>
           <t>https://www.samastore.qa/collections.json</t>
         </is>
@@ -6216,32 +7364,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" t="n">
+        <v>421</v>
+      </c>
+      <c r="G106" t="n">
+        <v>144</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="L106" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="M106" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="N106" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>https://www.sandro.qa/</t>
         </is>
@@ -6271,32 +7430,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" t="n">
+        <v>156</v>
+      </c>
+      <c r="G107" t="n">
+        <v>158</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>Men</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
+      <c r="L107" t="inlineStr">
         <is>
           <t>shopify</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
+      <c r="M107" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J107" t="inlineStr">
+      <c r="N107" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr">
+      <c r="O107" t="inlineStr">
         <is>
           <t>https://www.shop5.qa/</t>
         </is>
@@ -6328,30 +7498,40 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="K108" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="L108" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="M108" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="N108" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="O108" t="inlineStr">
         <is>
           <t>https://skylink.qa/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -6381,32 +7561,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" t="n">
+        <v>446</v>
+      </c>
+      <c r="G109" t="n">
+        <v>52</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="M109" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="N109" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="O109" t="inlineStr">
         <is>
           <t>https://soleil.qa/</t>
         </is>
@@ -6436,32 +7627,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" t="n">
+        <v>108</v>
+      </c>
+      <c r="G110" t="n">
+        <v>306</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="L110" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="M110" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="N110" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="O110" t="inlineStr">
         <is>
           <t>https://squatwolf.com/en-qa</t>
         </is>
@@ -6493,30 +7695,40 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr">
+      <c r="L111" t="inlineStr">
         <is>
           <t>Custom</t>
         </is>
       </c>
-      <c r="I111" t="inlineStr">
+      <c r="M111" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J111" t="inlineStr">
+      <c r="N111" t="inlineStr">
         <is>
           <t>Unverified – Qatar storefront live, purchase path not confirmed (JS/static page)</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>https://summer-salt.qa/</t>
         </is>
@@ -6546,32 +7758,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" t="n">
+        <v>442</v>
+      </c>
+      <c r="G112" t="n">
+        <v>2038</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="K112" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
+      <c r="L112" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="M112" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="N112" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="O112" t="inlineStr">
         <is>
           <t>https://swish.qa/collections.json</t>
         </is>
@@ -6603,30 +7826,40 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
+      <c r="L113" t="inlineStr">
         <is>
           <t>woocommerce</t>
         </is>
       </c>
-      <c r="I113" t="inlineStr">
+      <c r="M113" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J113" t="inlineStr">
+      <c r="N113" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr">
+      <c r="O113" t="inlineStr">
         <is>
           <t>https://tafaul.com.qa/</t>
         </is>
@@ -6656,32 +7889,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" t="n">
+        <v>278</v>
+      </c>
+      <c r="G114" t="n">
+        <v>325</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="K114" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
+      <c r="L114" t="inlineStr">
         <is>
           <t>Custom/Other</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr">
+      <c r="M114" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr">
+      <c r="N114" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr">
+      <c r="O114" t="inlineStr">
         <is>
           <t>https://www.thejacketmaker.qa/</t>
         </is>
@@ -6713,30 +7957,40 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="K115" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
+      <c r="L115" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr">
+      <c r="M115" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J115" t="inlineStr">
+      <c r="N115" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr">
+      <c r="O115" t="inlineStr">
         <is>
           <t>https://trendycorner.qa/collections.json</t>
         </is>
@@ -6764,32 +8018,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" t="n">
+        <v>24</v>
+      </c>
+      <c r="G116" t="n">
+        <v>21</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="K116" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
+      <c r="L116" t="inlineStr">
         <is>
           <t>salesforce-commerce</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr">
+      <c r="M116" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J116" t="inlineStr">
+      <c r="N116" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr">
+      <c r="O116" t="inlineStr">
         <is>
           <t>https://int.undiz.com/en_QA/</t>
         </is>
@@ -6821,30 +8086,40 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="K117" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="L117" t="inlineStr">
         <is>
           <t>WooCommerce</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="M117" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="N117" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
+      <c r="O117" t="inlineStr">
         <is>
           <t>https://vanillawear-qa.com/wp-json/wc/store/v1/products/categories</t>
         </is>
@@ -6874,32 +8149,43 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" t="n">
+        <v>961</v>
+      </c>
+      <c r="G118" t="n">
+        <v>224</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="K118" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
+      <c r="L118" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="M118" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
+      <c r="N118" t="inlineStr">
         <is>
           <t>Verified</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="O118" t="inlineStr">
         <is>
           <t>https://voilefashion.com/</t>
         </is>
@@ -6929,32 +8215,43 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" t="n">
+        <v>6615</v>
+      </c>
+      <c r="G119" t="n">
+        <v>2071</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
         <is>
           <t>Has clothing section</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="K119" t="inlineStr">
         <is>
           <t>Women, Men</t>
         </is>
       </c>
-      <c r="H119" t="inlineStr">
+      <c r="L119" t="inlineStr">
         <is>
           <t>Magento</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr">
+      <c r="M119" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
+      <c r="N119" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr">
+      <c r="O119" t="inlineStr">
         <is>
           <t>https://51east.com/</t>
         </is>
@@ -6984,32 +8281,43 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" t="n">
+        <v>245</v>
+      </c>
+      <c r="G120" t="n">
+        <v>113</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="K120" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H120" t="inlineStr">
+      <c r="L120" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I120" t="inlineStr">
+      <c r="M120" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J120" t="inlineStr">
+      <c r="N120" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr">
+      <c r="O120" t="inlineStr">
         <is>
           <t>https://www.haneenalsaify.com/products/soft-fit-cotton-hijab</t>
         </is>
@@ -7039,32 +8347,43 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" t="n">
+        <v>95</v>
+      </c>
+      <c r="G121" t="n">
+        <v>79</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="K121" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr">
+      <c r="L121" t="inlineStr">
         <is>
           <t>Shopify</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr">
+      <c r="M121" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
+      <c r="N121" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr">
+      <c r="O121" t="inlineStr">
         <is>
           <t>https://lusso-moda.com/products/first-light</t>
         </is>
@@ -7096,30 +8415,40 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="K122" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H122" t="inlineStr">
+      <c r="L122" t="inlineStr">
         <is>
           <t>Wix</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
+      <c r="M122" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J122" t="inlineStr">
+      <c r="N122" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr">
+      <c r="O122" t="inlineStr">
         <is>
           <t>https://www.sheikhastyle.com/perfumes</t>
         </is>
@@ -7146,32 +8475,43 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G123" t="n">
+        <v>1</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
         <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="K123" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr">
+      <c r="L123" t="inlineStr">
         <is>
           <t>Salla</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
+      <c r="M123" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J123" t="inlineStr">
+      <c r="N123" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr">
+      <c r="O123" t="inlineStr">
         <is>
           <t>https://www.shoplamees.com/product/abaya-aneqa-dantel</t>
         </is>
@@ -7203,30 +8543,40 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="K124" t="inlineStr">
         <is>
           <t>Unisex</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="L124" t="inlineStr">
         <is>
           <t>Zid</t>
         </is>
       </c>
-      <c r="I124" t="inlineStr">
+      <c r="M124" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J124" t="inlineStr">
+      <c r="N124" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr">
+      <c r="O124" t="inlineStr">
         <is>
           <t>https://threel.qa/products/</t>
         </is>
@@ -7258,30 +8608,40 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
           <t>Fashion-only</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="K125" t="inlineStr">
         <is>
           <t>Women</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t>Ecwid</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr">
+      <c r="M125" t="inlineStr">
         <is>
           <t>Small</t>
         </is>
       </c>
-      <c r="J125" t="inlineStr">
+      <c r="N125" t="inlineStr">
         <is>
           <t>Verified – StoreLeads gap check</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr">
+      <c r="O125" t="inlineStr">
         <is>
           <t>https://trendyqatar.com/products/search</t>
         </is>
@@ -9776,7 +11136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -10281,10 +11641,146 @@
         </is>
       </c>
     </row>
+    <row r="51"/>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
           <t>Method rules: sitemap counted in full (all child sitemaps followed); image and video sitemaps skipped; URLs deduplicated; Arabic and English URLs counted separately; when a sitemap is country-segmented only the listed market's pages are counted; fallbacks, used when no sitemap yields URLs, are the shop-page total, the platform product count (Shopify/WooCommerce) and the web archive (own host only); blocked or unreachable sites are marked Not available and left blank. Child sitemaps that failed are retried up to 4 times (5s/15s/45s/120s); if some still fail the row reads 'sitemap (partial: N of M sitemap files read)' and the count is a lower bound. If the sitemap has country segments but none for the listed market, the whole site is counted when a default storefront exists ('sitemap (whole site, no market segment)', which includes other-country URLs), otherwise the row is Not available.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>Organic traffic (Semrush)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Rows</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Filled with traffic</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>No data in Semrush</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Not checked (&lt;=500 pages)</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Not checked (other)</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>% of rows with a Semrush answer (traffic + no data)</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>64.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Rows with root-domain note (Semrush reported the parent root domain)</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Rows flagged as test/placeholder store (not deleted)</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Direct Semrush lookups for this file (domain_rank, MCP)</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Semrush organic traffic and keywords, database qa (batch results plus direct domain_rank lookups for domains missing from the batch)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Selection rule</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Checked when Website Pages Count is blank/non-numeric or &gt; 500; 500 pages or fewer are labelled 'Not checked (&lt;=500 pages)'</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Check date</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
         </is>
       </c>
     </row>
